--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -7526,7 +7526,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>POINT (36.80669999999999 6.358629999999989)</t>
+          <t>POINT (36.8067 6.35863)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2025-02-18T17:56:18</t>
+          <t>2026-09-28T16:38:45.222213</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2025-02-18T17:25:33.543975</t>
+          <t>2026-09-28T16:34:40.566444</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2025-02-18T14:49:49.019797</t>
+          <t>2026-09-28T16:32:37.590913</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -9714,7 +9714,11 @@
           <t>On 10 September 2023, storm Daniel reached its peak in north-eastern Libya, causing much damage and major destruction. One of the worst affected cities was Derna, at the time of the event home of 90,000 people. In the aftermath of the heavy rainfall the two ageing dams located in the Wadi Derna v...</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>On 10 September 2023, storm Daniel reached its peak in north-eastern Libya, causing much damage and major destruction. One of the worst affected cities was Derna, at the time of the event home of 90,000 people. In the aftermath of the heavy rainfall the two ageing dams located in the Wadi Derna valley, one just close to the city itself and one about 12 km southern along the river, collapsed not being able to resist the huge volume of water. This led to a catastrophic event in which large parts o Mitigation measures - low probability scenario Exposure assessment - high probability scenario Exposure assessment - medium probability scenario Exposure assessment - low probability scenario Reference dataset Flood hazard incorporating mitigation measues - high probability scenario Flood hazard incorporating mitigation measues - medium probability scenario Flood hazard incorporating mitigation measues - low probability scenario Mitigation measures - high probability scenario Mitigation measures - medium probability scenario</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10093,7 +10097,11 @@
           <t>In the wake of Storm Ciarn's destructive path across Western Europe from late October to early November 2023, the region of Tuscany in central Italy faced catastrophic flooding and landslides. On the 2 November 2023, an intense weather system hit Italy with strong scirocco winds and high precipit...</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>In the wake of Storm Ciarn's destructive path across Western Europe from late October to early November 2023, the region of Tuscany in central Italy faced catastrophic flooding and landslides. On the 2 November 2023, an intense weather system hit Italy with strong scirocco winds and high precipitations. The highest rainfall has occurred in the provinces of Pisa, Florence, Pistoia and Prato, the Bisenzio river and other minor secondary rivers overflowed and flooded neighboring localities. In Camp Mapbook Detailed Reference Dataset Detailed Reference Dataset Detailed Reference Dataset Mapbook Mapbook Mapbook Mapbook Detailed Damage Assessment Detailed Damage Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10204,7 +10212,12 @@
 According to the Cape Verde National Institute of Meteorology and Geophysics (I...</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard activation has been requested by DG ECHO ERCC to monitor the ground deformation occurring due to a seismic swarm event that started on 30 October 2023, in Brava Island, Cape Verde.
+According to the Cape Verde National Institute of Meteorology and Geophysics (INMG), seismicity at Brava Island increased on 30 October 2023 and remained elevated for several days. Continuous harmonic tremor emerged on 9 November and was interpreted as indicating the movement of ma Ground deformation analysis</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10262,27 +10275,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EMSN184</t>
+          <t>EMSN183</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Greece'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Flood in Thessaly Region, Greece</t>
+          <t>Forest fire impact assessment in Sierra de Los Guajares, Spain</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>POINT (23.19128 38.87509)</t>
+          <t>POINT (3.60201 36.85033)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10303,35 +10316,39 @@
         <v>1</v>
       </c>
       <c r="K178" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Wildfires are one of the main environmental hazards that regularly threaten the Iberian Peninsula. On 8 September 2022 a fire broke out in the Sierra de Los Gujares Granada province. It affected an estimated 5,194 hectares, mainly forest, and was only extinguished after 27 days. The aim of this activation is to qualify and quantify the effects of the forest fire on the Sierra de Los Gujares, through fire delineation and grading; an analysis of impacts on land cover, population, and assets; an as Los Guajares: P03 - Soil Erosion Risk - Scenario 2 Los Guajares: P03 - Soil Erosion Risk - Scenario 1 Los Guajares: P03 - Soil Erosion Risk - Scenario 0 Impact Assessment - Population and assets Impact Assessment - LULC Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>EMSN183</t>
+          <t>EMSN184</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Spain'}]</t>
+          <t>[{'short_name': 'Greece'}]</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Forest fire impact assessment in Sierra de Los Guajares, Spain</t>
+          <t>Flood in Thessaly Region, Greece</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>POINT (3.60201 36.85033)</t>
+          <t>POINT (23.19128 38.87509)</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -10352,10 +10369,15 @@
         <v>1</v>
       </c>
       <c r="K179" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>In September 2023, Thessaly Region, Greece, was hit by extended floods due to heavy rainfall. After three months, an area north, north-west of Karla lake is still flooded. The On-demand Mapping service has been activated toto provide the Ministry of Rural Development and Food with a delineation product of the current flooded area for the planning of the necessary recovery measures.
+Two Flood Delineation products (P04) have been generated to depict the current situation within the area of inte Flood Delineation- 18 December 2023 Flood Delineation- 19 December 2023</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10917,7 +10939,11 @@
           <t>On Monday 7 August 2023, Latvia experienced a severe storm characterised by large hailstones, thunderstorms, heavy precipitation, and intense winds. This event resulted in significant damage to human life, animals, the environment, properties, critical services, and business infrastructures. In a...</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>On Monday 7 August 2023, Latvia experienced a severe storm characterised by large hailstones, thunderstorms, heavy precipitation, and intense winds. This event resulted in significant damage to human life, animals, the environment, properties, critical services, and business infrastructures. In areas where hail was reported, harvests were damaged, and forestry zones also bore the brunt of the storm's impact. The State fire and rescue service of Latvia activated the CEMS On-demand Recovery Mappin</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11085,7 +11111,12 @@
           <t>The objective of EMSN181 activation is to assist the German Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Welthungerhilfe (WHH) in enhancing the identification of potential risks threatening livelihoods and food security in the Ishkashim area and Panj Rive...</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>The objective of EMSN181 activation is to assist the German Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Welthungerhilfe (WHH) in enhancing the identification of potential risks threatening livelihoods and food security in the Ishkashim area and Panj River valley along the border of Afghanistan and Tajikistan. The activation encompasses 17 areas of interest, with a combined area of 506.29 square kilometers.
+The products delivered for this activation are Mapbook</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11200,7 +11231,12 @@
 Since the risk imposed by landslides is st...</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery has been activated by the Administration for Civil Protection and Disaster Relief, on behalf of the Slovenian Environment Agency, following the landslides occurred in the Pasja Ravan region, in western Slovenia in August 2023.
+Since the risk imposed by landslides is still present in the area due to the typical autumn rain, the Authorised User has required further monitoring of the area.  By considering the statistical period of higher potential of landslide events, th Landslide - Situation as of 11/11/2023- P08.1 - Detailed damage assessment analyses over the affected area Landslide - Situation as of 11/11/2023- P08.1 - Detailed damage assessment analyses over the affected area Landslide - Situation as of 12/10/2023- P08.1 - Detailed damage assessment analyses over the affected area</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11257,7 +11293,11 @@
           <t>The landslides in Eastern Slovenia caused by heavy rainfalls on 17 May 2023 were object to investigate, geolocate and quantify using post event data of CEMS’s Aerial component. Very severe damages were caused by the slipping mud masses. Transportation networks and further infrastructure like elec...</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>The landslides in Eastern Slovenia caused by heavy rainfalls on 17 May 2023 were object to investigate, geolocate and quantify using post event data of CEMS’s Aerial component. Very severe damages were caused by the slipping mud masses. Transportation networks and further infrastructure like electricity or water supply are broken and interrupted. Even houses are affected and damaged/ destroyed. Considering the severity of the event besides this RRM-FLEX activation, further analysis were performe Mapbook</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11579,7 +11619,12 @@
           <t>The CEMS Risk and Recovery Standard has been activated by the German Federal Office of Civil Protection and Disaster Aid, in order to be provided with overview maps of a potential flood event affecting the city of Bremen in Germany. The requested products will be used for disaster management exer...</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard has been activated by the German Federal Office of Civil Protection and Disaster Aid, in order to be provided with overview maps of a potential flood event affecting the city of Bremen in Germany. The requested products will be used for disaster management exercises to prepare for real events.
+The scenario for the simulation has been provided by the Authorised User (AU): heavy rainfall (60 mm/h) hit the area during 10 hours, after a prolongated rainy period Modelled flood extent for major events Mapbook</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11689,7 +11734,11 @@
           <t>This CEMS Risk and Recovery Mapping (RRM) activation has been requested to provide damage delineation and grading product over the Parnitha Mountain, in the region of Attica (Greece), which was hit by a forest fire on 22nd August 2023, started around 11:56 (local time). According to the news, a w...</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>This CEMS Risk and Recovery Mapping (RRM) activation has been requested to provide damage delineation and grading product over the Parnitha Mountain, in the region of Attica (Greece), which was hit by a forest fire on 22nd August 2023, started around 11:56 (local time). According to the news, a wildfire started in a forest area near the monastery of Kleiston on Parnitha Mountain in Attica Region. The fire has led to the destruction of houses and vehicles in suburb of Fyli. The goal of the activa Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11742,7 +11791,12 @@
           <t>On the 22 August 2023, two wildfires started in a forest area near Prodromos village (Sterea Ellada Region) and in the afternoon in a forest area near Kyriaki village. The event lasted several days affecting a vast area and the residents of the villages Prodromos, Paralia Sarandi, Karioti, Tarsos...</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>On the 22 August 2023, two wildfires started in a forest area near Prodromos village (Sterea Ellada Region) and in the afternoon in a forest area near Kyriaki village. The event lasted several days affecting a vast area and the residents of the villages Prodromos, Paralia Sarandi, Karioti, Tarsos, Panagia Kalamiotissa and Agios Athanasios were ordered to evacuate.
+To be provided with information about the severity damage grade, the AU activated the Copernicus On-demand Mapping service, requesti Wildfire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11795,7 +11849,12 @@
           <t>On Monday 21 August morning (10:11 local time) a wildfire started in a forest area on Euboea island in Sterea Ellada Region, Greece. According to firefighters, the front was very broad and extended from Psachna to Artaki and Pissonas. The fire has burnt forest and farmland. To be provided with in...</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>On Monday 21 August morning (10:11 local time) a wildfire started in a forest area on Euboea island in Sterea Ellada Region, Greece. According to firefighters, the front was very broad and extended from Psachna to Artaki and Pissonas. The fire has burnt forest and farmland. To be provided with information about the severity damage grade, the AU activated the Copernicus On-demand Mapping service requesting the wildfire delineation and grading product (P07).
+The Wildfire delineation and grading p Wildfire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11848,7 +11907,11 @@
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the government of the Canary Islands (Spain), following the forest fire that broke out on the island of Tenerife (Canary Islands, Spain) on...</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the government of the Canary Islands (Spain), following the forest fire that broke out on the island of Tenerife (Canary Islands, Spain) on 15thof August 2023. It initially affected the municipalities of Arafo and Candelaria, extending to another 10 municipalities and affecting protected natural spaces such as the Teide National Park, La Cor Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11901,7 +11964,11 @@
           <t>In the early morning of 19 August 2023, a wildfire started in a forest area near Aristino village in the Greek regional unit of Evros, East Macedonia &amp; Thrace near the northeastern border with Turkey. Seven towns had to be evacuated a few hours after the declaration of the forest fire near the to...</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>In the early morning of 19 August 2023, a wildfire started in a forest area near Aristino village in the Greek regional unit of Evros, East Macedonia &amp; Thrace near the northeastern border with Turkey. Seven towns had to be evacuated a few hours after the declaration of the forest fire near the town of Alexandroupoli. The first evacuation order was directed towards the villages of Nipsa, Aetochori, and Pefka, followed by another message, sent around 4:00 p.m., which urged the evacuation of Loutro Fire Delineation and Grading - dNBR approach</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11959,7 +12026,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EMSR688</t>
+          <t>EMSR689</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11974,12 +12041,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Wildfire in Euboea Island, Greece</t>
+          <t>Wildfire in Rodopi, Greece</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>POINT (23.732529 38.452917)</t>
+          <t>POINT (25.504761 41.090738)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11989,7 +12056,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2023-11-28T09:47:05.454890</t>
+          <t>2023-11-28T09:27:40.534169</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -12001,10 +12068,10 @@
         <v>1</v>
       </c>
       <c r="J209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K209" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
@@ -12012,7 +12079,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EMSR689</t>
+          <t>EMSR688</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12027,12 +12094,12 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Wildfire in Rodopi, Greece</t>
+          <t>Wildfire in Euboea Island, Greece</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>POINT (25.504761 41.090738)</t>
+          <t>POINT (23.732529 38.452917)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -12042,7 +12109,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2023-11-28T09:27:40.534169</t>
+          <t>2023-11-28T09:47:05.454890</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -12054,10 +12121,10 @@
         <v>1</v>
       </c>
       <c r="J210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K210" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
@@ -12220,7 +12287,13 @@
 According to the news, firefight...</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>This CEMS Risk and Recovery Standard activation has been requested to provide damage delineation and grading product over the municipality of Portbou, in the region of Girona (Spain), which was hit by a forest fire on 04th August 2023, started around 14:30 (UTC).
+According to the news, firefighters from Spain's northeastern region of Catalonia teamed up with French colleagues as the blaze ravaged some 435 hectares (1,100 acres) of land, with an estimated 2,500 hectares threatened.
+The goal of  Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12379,7 +12452,12 @@
           <t>On 3 August 3 2023, a landslide hit the Georgian municipality of Oni in the mountains of the south Caucasian country of Georgia. The area is located in the Racha region, near the Russian border, about 140 kilometres northwest of the capital city Tbilisi. The landslide destroyed the resort area of...</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>On 3 August 3 2023, a landslide hit the Georgian municipality of Oni in the mountains of the south Caucasian country of Georgia. The area is located in the Racha region, near the Russian border, about 140 kilometres northwest of the capital city Tbilisi. The landslide destroyed the resort area of Shovi. On 10.08.2023, 21 casualties have been reported along with a further 18 missing as rescue efforts continue.
+This CEMS Risk and Recovery Standard activation has been requested to provide an analy Post-disaster Landslide Risk Assessment Post-disaster Soil Erosion Risk Assessment Detailed Damage Assessment Flood Delineation Land Use Land Cover dataset Reference dataset Digital Surface Model</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12697,7 +12775,11 @@
           <t>This CEMS Risk and Recovery Standard activation has been requested to provide damage delineation and grading product over Rhodes Island, Greece, which was hit by a wildfire on 18 July 2023, started around 16:00 UTC. Given the severity of the event, the Authorised User (AU) activated first the CEM...</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>This CEMS Risk and Recovery Standard activation has been requested to provide damage delineation and grading product over Rhodes Island, Greece, which was hit by a wildfire on 18 July 2023, started around 16:00 UTC. Given the severity of the event, the Authorised User (AU) activated first the CEMS Rapid Mapping. Through theEMSR675activation, delineation monitoring products have been delivered until 29th July, when a GeoEye-1 image showed no active flames in the area, leading the Rapid Mapping se Wildfire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12923,7 +13005,11 @@
           <t>The service request concerns Andalusia, a vast Spanish region spanning over 87,500 km² in Europe. Andalusia faces a multitude of natural and man-made hazards, including seismic events, tsunamis, floods, forest fires, and anthropogenic risks. It consists of eight provinces and 785 municipalities,...</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>The service request concerns Andalusia, a vast Spanish region spanning over 87,500 km² in Europe. Andalusia faces a multitude of natural and man-made hazards, including seismic events, tsunamis, floods, forest fires, and anthropogenic risks. It consists of eight provinces and 785 municipalities, boasting a coastline stretching nearly 1,000 kilometers, comprising both Mediterranean and Atlantic shores. Approximately 49% of Andalusia is covered by forested terrain. The activation requirements focu EAM EAM EAM EAM EAM EAM EAM EAM EAM</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13317,7 +13403,11 @@
           <t>Service request: The northern parts of Italy, mainly in the region of Emilia-Romagna, were heavily hit by torrential rainfall during the first half of May. The first event at the beginning of May triggered heavy flooding in particular around the cities of Bologna, Ravenna and Forlì-Cesena. A seco...</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Service request: The northern parts of Italy, mainly in the region of Emilia-Romagna, were heavily hit by torrential rainfall during the first half of May. The first event at the beginning of May triggered heavy flooding in particular around the cities of Bologna, Ravenna and Forlì-Cesena. A second heavy rainfall event hit the region on 16th of May. By that time, the ground was already saturated, and almost all rivers in the region were at historic high water level and more than 20 overflowing.  Landslide delineation and volume estimation in Emilia-Romagna, Italy</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13427,7 +13517,11 @@
           <t>The lack of electricity infrastructure &amp; services or the unreliability of these were identified in a World Bank Enterprise Survey of 2018 as one of the fourth biggest obstacle to commercial activities. To increase The Rwimi Hydroelectric Power Station in Uganda and the Mocuba Solar Power Station...</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>The lack of electricity infrastructure &amp; services or the unreliability of these were identified in a World Bank Enterprise Survey of 2018 as one of the fourth biggest obstacle to commercial activities. To increase The Rwimi Hydroelectric Power Station in Uganda and the Mocuba Solar Power Station in Mozambique electricity rates, two small-scale power generation installations were built. The activation focused on investigating the possibility to make use of satellite data to evaluate proxies for i Change Map T0 T1 Reference Map T3 Reference Map T3 Dam Break Scenario Human footprint - night-light changes T1-T2 Human footprint - night-light changes T1-T2 Human footprint - night-light changes T0-T3 Human footprint - night-light changes T0-T3 Human footprint - night-light changes T0-T1 Human footprint - night-light changes T0-T1</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13480,7 +13574,11 @@
           <t>Emilia Romagna region, Italy, has been hit by two severe flooding events within two weeks, starting from the first inundation occurred on 2ndMay 2023. On 16thof May, a new intense meteorological disturbance hit the same areas, where the intense precipitations raised river levels in the southern-e...</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Emilia Romagna region, Italy, has been hit by two severe flooding events within two weeks, starting from the first inundation occurred on 2ndMay 2023. On 16thof May, a new intense meteorological disturbance hit the same areas, where the intense precipitations raised river levels in the southern-eastern area of Emilia-Romagna. Historic highs have been reached in some rivers. The rains promoted the movement of hundreds of landslides in areas of the south-central regional Apennines (Romagna Apennin Mapbook Temporal analyses of occurred flood events Temporal analyses of occurred flood events Flood Delineation Flood Delineation</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13533,7 +13631,12 @@
           <t>Since the summer of 2022, Terceira Island is experiencing an increase in seismic events, mostly located around the Santa Brbara volcano. Due to the levels of microseismic activity, several evidences, and reports, the Azores Seismovolcanic Information and Surveillance Center (CIVISA) have declared...</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Since the summer of 2022, Terceira Island is experiencing an increase in seismic events, mostly located around the Santa Brbara volcano. Due to the levels of microseismic activity, several evidences, and reports, the Azores Seismovolcanic Information and Surveillance Center (CIVISA) have declared alert V2 (possible reactivation of the system).
+The Risk &amp; Recovery Mapping service has been activated by the Serviço Regional de Proteção Civil e Bombeiros dos Açores (SRPCBA) to support their activit</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13647,7 +13750,12 @@
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Administration for Civil Protection and Disaster Relief of the Republic of Slovenia on behalf of the Geological Survey of Slovenia and the University of Ljubljana following a severe rainfall episode that occurred in May 2023....</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Administration for Civil Protection and Disaster Relief of the Republic of Slovenia on behalf of the Geological Survey of Slovenia and the University of Ljubljana following a severe rainfall episode that occurred in May 2023. More than 1 100 landslides triggered in eastern Slovenia as a consequence of these heavy rainfalls. The goal of the activation is to assess the risk of soil erosion and landslide in eastern Slovenia.
+W Post-disaster Landslide Risk Assessment Post-disaster Landslide Risk Assessment Post-disaster Soil Erosion Risk Assessment Post-disaster Soil Erosion Risk Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14152,7 +14260,11 @@
           <t>During the evening of 14/03/2023, a forest fire started in the Natura 2000 area of La Balsa del Pulguer. The protected area of Balsa del Pulguer is home to valuable and threatened species and habitats, serving as a site for recreational activities. With the aim of quantifying and qualifying the e...</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>During the evening of 14/03/2023, a forest fire started in the Natura 2000 area of La Balsa del Pulguer. The protected area of Balsa del Pulguer is home to valuable and threatened species and habitats, serving as a site for recreational activities. With the aim of quantifying and qualifying the effects of this forest fire, including loss estimations and changed risk assessment, theCopernicus Aerial Componentwas deployed providing ortho-rectified images RGB/NIR GSD 5 cm, photogrammetric point clo Soil Erosion Risk Biomass Loss Assessment Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14258,7 +14370,11 @@
           <t>In August 2022, a wild forest fire affected the Portuguese Serra da Estrela National Park for several days, with strong winds and high temperatures making it difficult for firefighters to control the flames. The Copernicus Emergency Management Service Rapid Mapping (EMSR618) was activated to resp...</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>In August 2022, a wild forest fire affected the Portuguese Serra da Estrela National Park for several days, with strong winds and high temperatures making it difficult for firefighters to control the flames. The Copernicus Emergency Management Service Rapid Mapping (EMSR618) was activated to respond to this event. The fire, the largest in 50 years, resulted in an affected area of about 25,000 hectares, forced the evacuation of several local communities, and caused significant damage to the natur Soil loss Soil loss Soil loss Landslide risk Landslide risk Erosion risk Erosion risk Erosion risk Assessment and accessibility of the road network Assessment of vegetation recovery</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14539,7 +14655,11 @@
           <t>On 27 November 2022, a landslide occurred in the municipality of Casamicciola on the island of Ischia, Italy, which affected 28.2 hectares of land. The incident was triggered by heavy rainfall, with more than 120 mm recorded within six hours. The landslide occurred between 03:00 and 05:00 am, res...</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>On 27 November 2022, a landslide occurred in the municipality of Casamicciola on the island of Ischia, Italy, which affected 28.2 hectares of land. The incident was triggered by heavy rainfall, with more than 120 mm recorded within six hours. The landslide occurred between 03:00 and 05:00 am, resulting in 12 fatalities and several hundred injuries. In response to the disaster, Italy declared a state of emergency, and the Italian National Department of Civil Protection activated the Copernicus Ra Coastal erosion hazard analysis Ground motion detection UP Ground motion detection EW Potential economic loss due to landslide risk Assets map Landslide risk assessment Landslide exposure and vulnerability assessment Landslide hazard assessment Estimation of economic loss Reference mapping</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15024,7 +15144,12 @@
           <t>The CEMS Risk and Recovery Mapping service has been activated for an assessment of the extent of floods that occurred in October 2022 in the Lake Chad area. The request included projections and an analysis of the difference between seasonal/structural and extraordinary (one-off) precipitations an...</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Mapping service has been activated for an assessment of the extent of floods that occurred in October 2022 in the Lake Chad area. The request included projections and an analysis of the difference between seasonal/structural and extraordinary (one-off) precipitations and floods in the area.
+On 19 October 2022 the head of the Chad government declared a state of emergency in the country in response to flooding in 636 localities across 18 of the country’s 23 provinces. T Water depth Wet season Water depth Wet season Water depth Wet season Water depth Dry season Water depth Dry season Water depth Dry season Water depth Water depth Water depth Flood Delineation</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15077,7 +15202,11 @@
           <t>The CEMS Risk and Recovery Standard has been activated for the analysis of the flood occurred in September 2022 in Bulgaria, in the villages of Bogdan and Karavelovo, in Karlovo Municipality.From the 2nd of September 2022, torrential rainfalls caused rivers and streams to overflow flooding severa...</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard has been activated for the analysis of the flood occurred in September 2022 in Bulgaria, in the villages of Bogdan and Karavelovo, in Karlovo Municipality.From the 2nd of September 2022, torrential rainfalls caused rivers and streams to overflow flooding several villages in Plovdiv Province including Bogdan, Rozino, Karavelovo, Stoletovo, Pesnopoi and Trilistnik and the flooding reached a depth from 1.5m to 2m in some areas.Local media reported that the entire Temporal analyses of occurred flood events Temporal analyses of occurred flood events Reference Dataset Mapbook</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15501,7 +15630,11 @@
           <t>The CEMS Risk and Recovery Standard has been activated for a retrospective assessment of an extreme flooding across Western Europe in summer 2021, which had devastating impacts on Luxembourg. Institute MeteoLux, the Luxembourgish meteorological institute, reported torrential rains broke two recor...</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard has been activated for a retrospective assessment of an extreme flooding across Western Europe in summer 2021, which had devastating impacts on Luxembourg. Institute MeteoLux, the Luxembourgish meteorological institute, reported torrential rains broke two records for the month of July at the weather station at Luxembourg-Findel Airport. The maximum precipitation in 12 hours and 24 hours reached accumulations of 74.2 mm and 79.4 mm, beating the previous records Mapbook Mapbook Temporal analyses of occurred flood events Temporal analyses of occurred flood events Temporal analyses of occurred flood events Temporal analyses of occurred flood events Flood Delineation Flood Delineation Flood Delineation Flood Delineation</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15550,7 +15683,11 @@
         <v>44</v>
       </c>
       <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>The scope of this activation is to continue and update the analysis already performed under CEMS-FLEX activations EMSN063, EMSN083 and EMSN113, providing information about the agriculture, food security and nutrition analysis situation in Northern Nigeria, in support of the WFP officers. For the 4th edition, it was required to analyse 44 AOIs (33 to be updated and 11 newly analysed) distributed between four Nigerian States: 35 AOIs located at the north-western region and 9 AOIs at the north-east Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15807,7 +15944,12 @@
         <v>2</v>
       </c>
       <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the “Área de Coordinación de Emergencias y Protección Civil de Ceuta” following the forest fire that broke out in the Autonomous City of Ceuta (Spain) on 09 September 2022. The goal of the activation is to provide wildfire damage delineation and grading products and to assess the post-disaster erosion risk.
+TheP07-Wildfire delineation and gradingprod Post-disaster Soil Erosion Risk Assessment Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16068,7 +16210,11 @@
           <t>The activation was triggered due to a massive fish die-off in the Odra (Oder) river beginning in late July 2022 in the upstream area around the village of Lipki and moving downstream to Kostrzyn nad Odrą, where dead fishes were encountered at 10th of August 2022. The activation aims to provide a...</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>The activation was triggered due to a massive fish die-off in the Odra (Oder) river beginning in late July 2022 in the upstream area around the village of Lipki and moving downstream to Kostrzyn nad Odrą, where dead fishes were encountered at 10th of August 2022. The activation aims to provide a water quality information layer based on a Sentinel 2 analysis for 1) the most recent situation around the city of Wrocław and 2) the evolution during the summer period of 2022 in comparison to 2021 and  Chlorophyll-a concentration 2022 Chlorophyll-a concentration 2021 Chlorophyll-a concentration 2020 Total suspended matter Chlorophyll-a concentration</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16712,7 +16858,12 @@
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the government of Castilla y León region (Spain), following the forest fire that broke out in the municipalities of San Juan de la Nava and...</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr"/>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the government of Castilla y León region (Spain), following the forest fire that broke out in the municipalities of San Juan de la Nava and El Barraco (Ávila) on 24th of July 2022. The goal of the activation is to provide wildfire damage delineation and grading products and to assess the post-disaster erosion risk.
+The fire reached the Leve Post-disaster Soil Erosion Risk Assessment Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16819,7 +16970,12 @@
 According to the news,...</t>
         </is>
       </c>
-      <c r="M298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>This CEMS Risk and Recovery Standard activation has been requested to provide damage delineation and grading product over the municipality of Carcastillo, in the region of Navarra (Spain), which was hit by a forest fire on 25th July 2022, started around 13:20 (local time).
+According to the news, the forest fire was most probably arson and hit a pine forest and several fields that had already been cut. The Level 2 of the Forest Fire Emergency Plan has been activated and a large number of firefig Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16982,7 +17138,11 @@
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fires that broke out in the municipali...</t>
         </is>
       </c>
-      <c r="M301" t="inlineStr"/>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fires that broke out in the municipalities of Casas de Miravete and Jerte – Caceres, in the region of Extremadura (Spain), between 14 and 16 July 2022. Several hectares of the Monfragüe National park and the Reserva Natural de la Garganta de Fire Delineation and Grading Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -18594,7 +18754,12 @@
           <t>CEMS Risk and Recovery Mapping service has been activated by DG Joint Research Centre with the aim to source high-quality reference dataset to establish the new Exposure Mapping component of the Copernicus Emergency Management Service. The outputs of this activation will be used for the establish...</t>
         </is>
       </c>
-      <c r="M330" t="inlineStr"/>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>CEMS Risk and Recovery Mapping service has been activated by DG Joint Research Centre with the aim to source high-quality reference dataset to establish the new Exposure Mapping component of the Copernicus Emergency Management Service. The outputs of this activation will be used for the establishment of the service (including tender preparation and eventually assessment), Global Human Settlement Layer2 (GHSL) validation, and training.
+The analysis will focus on 5 sample areas distributed across</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -18877,7 +19042,11 @@
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
         </is>
       </c>
-      <c r="M335" t="inlineStr"/>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Arguedas and Valtierra in the region of Navarra (Spain), on 18thJune 2022. It affected several grain fields, coniferous forest, several warehouses and a nature amusement park, where more than Wildfire delineation and grading</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -19274,7 +19443,11 @@
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the region of A...</t>
         </is>
       </c>
-      <c r="M342" t="inlineStr"/>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the region of Andalucía (Spain) on 7thof June 2022. Within the municipalities of Pujerra, Juzcar and Benahavís (Mlaga) more than 5,000 hectares of wooden areas have burnt. The goal of the activation is to provide wildf Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -19555,7 +19728,12 @@
           <t>The island of São Jorge in the Azores archipelago (Portugal) has been on a V4 high alert since the 23rd March 2022 due to a seismic-volcanic crisis that started on the 19th of the same month, located from Ponta dos Rosais to Norte Pequeno - Silveira area. The most energetic earthquake of this cri...</t>
         </is>
       </c>
-      <c r="M347" t="inlineStr"/>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>The island of São Jorge in the Azores archipelago (Portugal) has been on a V4 high alert since the 23rd March 2022 due to a seismic-volcanic crisis that started on the 19th of the same month, located from Ponta dos Rosais to Norte Pequeno - Silveira area. The most energetic earthquake of this crisis occurred on March 29th, with an epicenter at about 2 km SSW of Velas and a magnitude of 3.8 (Richter). So far, around 271 earthquakes felt by the population have been identified.
+Under such circunst Exposure Map Exposure Map Exposure Map Exposure Map Exposure Map Exposure Map Exposure Map Exposure Exposure Map Exposure Map</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -19608,7 +19786,12 @@
           <t>This Copernicus EMS Risk &amp; Recovery Mapping STD activation was triggered by Federal Office of Civil Protection and Disaster Assistance (BBK), Germany on behalf of The Technical Relief Agency (THW) that is active in Iraq since November 2013. One of the main use would be to support a joint exercise...</t>
         </is>
       </c>
-      <c r="M348" t="inlineStr"/>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>This Copernicus EMS Risk &amp; Recovery Mapping STD activation was triggered by Federal Office of Civil Protection and Disaster Assistance (BBK), Germany on behalf of The Technical Relief Agency (THW) that is active in Iraq since November 2013. One of the main use would be to support a joint exercise with local authorities in Bagdad and Erbil, region north of Bagdad.
+The first exercise aims at simulating a dam breach at Lake Hamrin (north of Bagdad and the city of Baqubah). THW would like to know w Dam break simulation - Mapbook Dam break simulation Reference map - Mapbook Reference map - Mapbook Reference map Reference map</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -19661,7 +19844,11 @@
           <t>The present activation aims at supporting the Greece National Secretariat for Civil Protection to develop civil protection plans for archaeological sites facing climate change and its effects with amulti-risk analysis. It focusses on two major Greek archaeological sites and UNESCO World Heritage...</t>
         </is>
       </c>
-      <c r="M349" t="inlineStr"/>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>The present activation aims at supporting the Greece National Secretariat for Civil Protection to develop civil protection plans for archaeological sites facing climate change and its effects with amulti-risk analysis. It focusses on two major Greek archaeological sites and UNESCO World Heritage sites,Delphi and Ancient Olympia, both being prone to the below-mentioned multitude of natural hazards that are most likely to intensify and become more extreme under the impact of climate change. Result Evacuation Plan Forest Fire Evacuation Plan Forest Fire Evacuation Plan Flood Evacuation Plan Flood Evacuation Plan Earthquake Evacuation Plan Earthquake Plain Flood Risk Scenario 01 Plain Flood Risk Scenario 01 Plain Flood Risk Scenario 01 Plain Flood Risk Scenario 01</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -20109,7 +20296,11 @@
           <t>BEAM (Basic European Assets Map) provides a spatial data package for the estimation and comparison of real and potential damages caused by natural disasters. BEAM is based on spatial and statistical data available throughout Europe (Corine Land Cover, Urban Atlas) and enriched by national statist...</t>
         </is>
       </c>
-      <c r="M357" t="inlineStr"/>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>BEAM (Basic European Assets Map) provides a spatial data package for the estimation and comparison of real and potential damages caused by natural disasters. BEAM is based on spatial and statistical data available throughout Europe (Corine Land Cover, Urban Atlas) and enriched by national statistics information. The data model follows an approach, that can be applied across Europe, and is scalable from local to regional and national analysis. Data are stored as assets in monetary values per area BEAM Austria BEAM Austria BEAM Austria BEAM Austria BEAM Austria BEAM Austria BEAM Austria BEAM Austria BEAM Austria BEAM Austria</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -20215,7 +20406,11 @@
         <v>1</v>
       </c>
       <c r="L359" t="inlineStr"/>
-      <c r="M359" t="inlineStr"/>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>The activation aims to support Deutsche Welthungerhilfe e. V. within the context of hazard identification and management activities by providing detailed information on infrastructure (buildings and road network) and agricultural activity (field delineation, crop mapping, and productivity), in order to better identify potential risks that may endanger food security, and mitigation measures that enable better resilience in the fragile environment of the AOIs. The AOIs are located in the Badakhsha Mapbook</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -20547,7 +20742,11 @@
           <t>On September 19th 2021, an eruption on the Cumbre Vieja volcanic ridge started southwest of La Palma, Canary Island, Spain. After 85 days of activity, it stopped on December 13th 2021 and the eruption was officially declared to have ended on December 25th, 2021. Over 7,000 people were evacuated a...</t>
         </is>
       </c>
-      <c r="M365" t="inlineStr"/>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>On September 19th 2021, an eruption on the Cumbre Vieja volcanic ridge started southwest of La Palma, Canary Island, Spain. After 85 days of activity, it stopped on December 13th 2021 and the eruption was officially declared to have ended on December 25th, 2021. Over 7,000 people were evacuated and the lava flow covered an area of about 3.5 km at its widest point and 6.2 km long, affecting over 1,200 hectares. It reached the sea in two different locations forming two new peninsulas. During the e Lava Flow Volume T2 to T1 Lava Flow Volume T1 Elevation Change T2 to T1 Digital Elevation Model T1 Lava Flow Volume T3 Elevation Change T3 to T0 Digital Elevation Model T3 Lava Flow Volume T2 Elevation Change T2 to T0 Digital Elevation Model T2</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -20714,7 +20913,11 @@
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the European Commission DG ECHO, on behalf of the World Food Programme (WFP) Mozambique, with the final objective to improve food security in the northern provinces of Cabo Delgado, Nampula and Niassa. To reach this goal, WFP wil...</t>
         </is>
       </c>
-      <c r="M368" t="inlineStr"/>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the European Commission DG ECHO, on behalf of the World Food Programme (WFP) Mozambique, with the final objective to improve food security in the northern provinces of Cabo Delgado, Nampula and Niassa. To reach this goal, WFP will conduct an exercise to assess vulnerabilities of IDPs and their hosting communities. One of the target population is the one living in the urban area of Pemba, for which the user requires detailed maps Mapbook Reference Dataset</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -20767,7 +20970,11 @@
           <t>The CEMS Risk and Recovery Mapping service has been newly activated to continue monitoring the ground deformation of La Palma island (Cumbre Vieja region), Spain, after the end of the eruption phase (started on 19 September 2021 and ended on 25 December 2021). The eruption period has been the lon...</t>
         </is>
       </c>
-      <c r="M369" t="inlineStr"/>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Mapping service has been newly activated to continue monitoring the ground deformation of La Palma island (Cumbre Vieja region), Spain, after the end of the eruption phase (started on 19 September 2021 and ended on 25 December 2021). The eruption period has been the longest on the island since records began. Voluminous lava flows reached populated areas, fanning out across settlements and banana plantations, destroying thousands of buildings, and ultimately pouring ove Ground deformation analysis Landslide risk assessment Soil erosion risk assessment Land Use Land Cover - CLC Update</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -20873,7 +21080,13 @@
         <v>0</v>
       </c>
       <c r="L371" t="inlineStr"/>
-      <c r="M371" t="inlineStr"/>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard has been activated by the Norwegian Refugee Council (NRC).
+The objective of this activation is to generate products that will enable humanitarian actors to understand the situation in the area.
+This activation is sensitive, so no product or result will be published.</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -20927,7 +21140,12 @@
 No product that resulted from this activation will...</t>
         </is>
       </c>
-      <c r="M372" t="inlineStr"/>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>The Spanish General Directorate of Civil Protection and Emergencies (CENEM) has triggered the Copernicus Emergency Management Service (CEMS) Risk and Recovery Mapping to develop tsunami risk analysis along the Mediterranean coast of Andalusia.
+No product that resulted from this activation will be released to the public.</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -21033,7 +21251,12 @@
         <v>1</v>
       </c>
       <c r="L374" t="inlineStr"/>
-      <c r="M374" t="inlineStr"/>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>This request comes in the framework of the Syria Urban Recovery Framework Project developed by the EU Delegation, UN-Habitat and partners. The aim is to provide detailed mapping of the damage assessment of buildings and reconstruction monitoring in urban areas in Syria.
+The maps will be used in the frame of the above-mentioned project, to better assess the needs in terms of shelter recovery and future reconstruction when a political settlement is firmly underway. Reconstruction monitoring</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -21086,7 +21309,12 @@
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by DG ECHO (Directorate-General for European Civil Protection and Humanitarian Aid Operations) as Authorized User (AU), on behalf of the Norwegian Refugee Council (Sudan) as the End User (EU). The objective of the activation is to a...</t>
         </is>
       </c>
-      <c r="M375" t="inlineStr"/>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by DG ECHO (Directorate-General for European Civil Protection and Humanitarian Aid Operations) as Authorized User (AU), on behalf of the Norwegian Refugee Council (Sudan) as the End User (EU). The objective of the activation is to assess areas in Sudan hit by humanitarian crisis.
+This activation is sensitive, so no product or result will be published.</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -21192,7 +21420,11 @@
         <v>66</v>
       </c>
       <c r="L377" t="inlineStr"/>
-      <c r="M377" t="inlineStr"/>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>The scope of the activation is to support the WFP officers with geospatial analysis regarding the agriculture and food security situation and nutrition analysis in 57 AOIs, including the update for 5 AOIs that were already analysed under activation EMSN-063 and EMSN-083, spread between nine Nigerian States: 36 AOIs located at the north-western region (NW) and 21 AOIs at the north-eastern (NE) of Nigeria, near Lake Chad. Due to the inaccessibility of the region caused by on-going armed conflicts, Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change Crop Change</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -21648,7 +21880,11 @@
           <t>The CEMS Risk and Recovery Standard activation has been initially requested to monitor the ground deformation occurring due to a seismic swarm event that started on the 11thSeptember 2021, in the southern side of La Palma island (Cumbre Vieja region), Spain. In the following days, thousands of sm...</t>
         </is>
       </c>
-      <c r="M385" t="inlineStr"/>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery Standard activation has been initially requested to monitor the ground deformation occurring due to a seismic swarm event that started on the 11thSeptember 2021, in the southern side of La Palma island (Cumbre Vieja region), Spain. In the following days, thousands of small earthquakes and ground deformation phenomena were indicating that there was restless magma under the ground. Hence, on the 14thSeptember, the emergency plan PEVOLCA (Plan de Prevención del Riesgo Vol Ground deformation analysis Landslide risk assessment Landslide risk assessment Soil erosion risk assessment Soil erosion risk assessment</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -21703,7 +21939,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard has been activated by EEAS (European External Action Service) on behalf of the World Bank Group in order to support EU Delegation, World Bank, UN and AfDB in a Recovery and Peace Building Assessment. This aims at understanding causes of the conflict in the North of Mozambique, and at developing a strategy for future Government’s intervention in the area. The ongoing conflict in Cabo Delgado Province started in October 2017 with attacks by insurgents. The attac P19-Population displacement location P19-Population displacement location P19-Population displacement location P19-Population displacement location P19-Population displacement location P03.5-Land Use and Land Cover: CLC New @1:25000 P03.5-Land Use and Land Cover: CLC New @1:25000 P03.5-Land Use and Land Cover: CLC New @1:25000 P03.5-Land Use and Land Cover: CLC New @1:25000 P03.5-Land Use and Land Cover: CLC New @1:25000</t>
+          <t>The CEMS Risk and Recovery Standard has been activated by EEAS (European External Action Service) on behalf of the World Bank Group in order to support EU Delegation, World Bank, UN and AfDB in a Recovery and Peace Building Assessment. This aims at understanding causes of the conflict in the North of Mozambique, and at developing a strategy for future Government’s intervention in the area. The ongoing conflict in Cabo Delgado Province started in October 2017 with attacks by insurgents. The attac Mapbook Population displacement location Population displacement location Population displacement location Population displacement location Population displacement location Population displacement location Population displacement location Population displacement location Population displacement location</t>
         </is>
       </c>
     </row>
@@ -21824,7 +22060,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>EMSN109</t>
+          <t>EMSN110</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -21839,12 +22075,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Wildfire in Alcaracejos, Spain</t>
+          <t>Wildfire in Alburquerque, Spain</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>POINT (-4.94932 38.2282)</t>
+          <t>POINT (-6.85472 40.02093)</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -21874,7 +22110,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -21931,14 +22167,14 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>EMSN110</t>
+          <t>EMSN109</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -21953,12 +22189,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Wildfire in Alburquerque, Spain</t>
+          <t>Wildfire in Alcaracejos, Spain</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>POINT (-6.85472 40.02093)</t>
+          <t>POINT (-4.94932 38.2282)</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -21988,7 +22224,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -22045,7 +22281,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out over the municipality of Ezcaray in La Rioja region (North-Eastern Spain), started on the 21stAugust 2021 at about 13:20 (local time) and it was extinguished on the 23rdAugust. More than 100 hectares were affected in the  P07 Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out over the municipality of Ezcaray in La Rioja region (North-Eastern Spain), started on the 21stAugust 2021 at about 13:20 (local time) and it was extinguished on the 23rdAugust. More than 100 hectares were affected in the  Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22796,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard has been activated for a retrospective assessment of the flood event that took place in Solingen (North Rhine Westphalia area, Germany). A series of storm events throughout June and July 2021 left the ground saturated, followed by heavy rainfalls from the 12thJuly and particularly on the 14thJuly 2021. A severe flood event occurred over the next few days along the Moselle, Rhine and Ruhr rivers. The Germany’s weather service Deutscher Wetterdienst (DWD) report P04-Flood Delineation P04-Flood Delineation P06-Temporal analyses of occurred flood events P06-Temporal analyses of occurred flood events</t>
+          <t>The CEMS Risk and Recovery Standard has been activated for a retrospective assessment of the flood event that took place in Solingen (North Rhine Westphalia area, Germany). A series of storm events throughout June and July 2021 left the ground saturated, followed by heavy rainfalls from the 12thJuly and particularly on the 14thJuly 2021. A severe flood event occurred over the next few days along the Moselle, Rhine and Ruhr rivers. The Germany’s weather service Deutscher Wetterdienst (DWD) report Temporal analyses of occurred flood events Temporal analyses of occurred flood events Flood Delineation Flood Delineation</t>
         </is>
       </c>
     </row>
@@ -23312,27 +23548,27 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>EMSN102</t>
+          <t>EMSN103</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Spain'}]</t>
+          <t>[{'short_name': 'Central African Republic'}]</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Wildfires in Huelva, Spain</t>
+          <t>IDP camp monitoring in Bria, Central African Republic</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>POINT (-6.61875 37.43943)</t>
+          <t>POINT (21.9657 6.54857)</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -23353,43 +23589,43 @@
         <v>1</v>
       </c>
       <c r="K415" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d Population displacement location Overview Map Overview Map Population displacement location</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EMSN103</t>
+          <t>EMSN102</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Central African Republic'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>IDP camp monitoring in Bria, Central African Republic</t>
+          <t>Wildfires in Huelva, Spain</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>POINT (21.9657 6.54857)</t>
+          <t>POINT (-6.61875 37.43943)</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -23410,16 +23646,16 @@
         <v>1</v>
       </c>
       <c r="K416" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23540,7 +23776,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EMSN101</t>
+          <t>EMSN100</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -23555,12 +23791,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Wildfire in Ciudad Real, Spain</t>
+          <t>Wildfires in La Rioja, Spain</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>POINT (-4.85493 38.75007)</t>
+          <t>POINT (-2.01861 42.15347)</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -23585,19 +23821,19 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>EMSN100</t>
+          <t>EMSN101</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -23612,12 +23848,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Wildfires in La Rioja, Spain</t>
+          <t>Wildfire in Ciudad Real, Spain</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>POINT (-2.01861 42.15347)</t>
+          <t>POINT (-4.85493 38.75007)</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -23642,12 +23878,12 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23985,7 +24221,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>BEAM (Basic European Assets Map) provides a spatial data package for the estimation and comparison of real and potential damages caused by natural disasters. BEAM is based on spatial and statistical data available throughout Europe (Corine Land Cover, Urban Atlas) and enriched by national statistics information. The data model follows an approach, that can be applied across Europe, and is scalable from local to regional and national analysis. Data are stored as assets in monetary values per area BEAM Sweden BEAM Sweden (Detail, Tile 21) BEAM Sweden (Detail, Tile 20) BEAM Sweden (Detail, Tile 19) BEAM Sweden (Detail, Tile 18) BEAM Sweden (Detail, Tile 17) BEAM Sweden (Detail, Tile 16) BEAM Sweden (Detail, Tile 15) BEAM Sweden (Detail, Tile 14) BEAM Sweden (Detail, Tile 13)</t>
+          <t>BEAM (Basic European Assets Map) provides a spatial data package for the estimation and comparison of real and potential damages caused by natural disasters. BEAM is based on spatial and statistical data available throughout Europe (Corine Land Cover, Urban Atlas) and enriched by national statistics information. The data model follows an approach, that can be applied across Europe, and is scalable from local to regional and national analysis. Data are stored as assets in monetary values per area BEAM Sweden BEAM Sweden BEAM Sweden BEAM Sweden BEAM Sweden BEAM Sweden BEAM Sweden BEAM Sweden BEAM Sweden BEAM Sweden</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24391,13 @@
 The event was a 3km wide wildfire in the Mourne Mountains of County Down which ran from 23 April...</t>
         </is>
       </c>
-      <c r="M429" t="inlineStr"/>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>The CEMS Risk and Recovery STANDARD has been activated by the EU Delegation to UK and Northern Ireland as Authorized User (AU), on behalf of the End User (EU) that is the Northern Ireland Executive.
+The event was a 3km wide wildfire in the Mourne Mountains of County Down which ran from 23 April (start) to 25 April 2021 (main fires extinguished).
+This activation aimed at delineating the extent of the fire trough the RRM STANDARD productwildfire delineation and grading (P07)and providing an esti Fire Delineation and Grading</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -24210,7 +24452,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard has been activated by EEAS (European External Action Service) on behalf of the World Bank Group in order to support EU Delegation, World Bank, UN and AfDB in a Recovery and Peace Building Assessment. This aims at understanding causes of the conflict in the North of Mozambique, and at developing a strategy for future Government’s intervention in the area. The ongoing conflict in Cabo Delgado Province started in October 2017 with attacks by insurgents. The attac P19-Population displacement location-MONIT02 P19-Population displacement location Mapbook-P19-Overview Map Mapbook-P19-Overview Map Mapbook-P19-Overview Map Mapbook-P19-Overview Map Mapbook-P19-Overview Map Mapbook-P19-Overview Map Mapbook-P19-MONIT03-Overview Map P19-Population displacement location-MONIT03</t>
+          <t>The CEMS Risk and Recovery Standard has been activated by EEAS (European External Action Service) on behalf of the World Bank Group in order to support EU Delegation, World Bank, UN and AfDB in a Recovery and Peace Building Assessment. This aims at understanding causes of the conflict in the North of Mozambique, and at developing a strategy for future Government’s intervention in the area. The ongoing conflict in Cabo Delgado Province started in October 2017 with attacks by insurgents. The attac Population displacement location Mapbook Mapbook Population displacement location Population displacement location Population displacement location Population displacement location Population displacement location Population displacement location Mapbook</t>
         </is>
       </c>
     </row>
@@ -24575,27 +24817,27 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>EMSN091</t>
+          <t>EMSN093</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Philippines'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
+          <t>{'slug': 'mass', 'name': 'Mass Movement'}</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Assessing changes in subsidence rates in the low Pampanga river basin and Manila area, Philippines</t>
+          <t>Rockfall risk analysis in Valle Gran Rey, La Gomera (Spain)</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>POINT (120.7985 14.78801)</t>
+          <t>POINT (-17.31476 28.102249999999998)</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -24603,10 +24845,14 @@
           <t>2021-04-30T01:00:00</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2026-01-20T10:00:57.435407</t>
+        </is>
+      </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>recovery</t>
+          <t>preparedness</t>
         </is>
       </c>
       <c r="I437" t="b">
@@ -24616,77 +24862,73 @@
         <v>1</v>
       </c>
       <c r="K437" t="n">
-        <v>1</v>
-      </c>
-      <c r="L437" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering i...</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
-        <is>
-          <t>The service was activated by a request from the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) – authorized user, and the University of Philippines – local user. Several sources suggest that the Manila NCR and lower Pampanga river basin, Philippines, has been affected by ground subsidence phenomena impacting settlements and increasing flood risk.
-The EMS service aims to provide evidence of ground motion Ground Deformation – Overview key map (Overview A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>EMSN093</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Spain'}]</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>{'slug': 'mass', 'name': 'Mass Movement'}</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>Rockfall risk analysis in Valle Gran Rey, La Gomera (Spain)</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>POINT (-17.31476 28.102249999999998)</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>2021-04-30T01:00:00</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>2026-01-20T10:00:57.435407</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>preparedness</t>
-        </is>
-      </c>
-      <c r="I438" t="b">
-        <v>1</v>
-      </c>
-      <c r="J438" t="n">
-        <v>1</v>
-      </c>
-      <c r="K438" t="n">
-        <v>6</v>
-      </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering i...</t>
-        </is>
-      </c>
-      <c r="M438" t="inlineStr">
         <is>
           <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering information on the potential hazard of the area, to carry out the adequate management plans.
 The products resulting from this activation are:
 Product 2
-Pre-event DEM extracted using photogrammetr Rockfall hazard. Overview key map (Overview A1) Rockfall asset and population risk (low season). Overview key map (Overview A1) Rockfall asset and population risk (high season). Overview key map (Overview A1) Rockfall asset and population exposure. Overview key map (Overview A1) Reference. Overview key map (Overview A1) Ground Deformation. Overview key map (Overview A1)</t>
+Pre-event DEM extracted using photogrammetr Rockfall hazard. Overview key map Rockfall asset and population risk (low season). Overview key map Rockfall asset and population risk (high season). Overview key map Rockfall asset and population exposure. Overview key map Reference. Overview key map Ground Deformation. Overview key map</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>EMSN091</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Philippines'}]</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Assessing changes in subsidence rates in the low Pampanga river basin and Manila area, Philippines</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>POINT (120.7985 14.78801)</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2021-04-30T01:00:00</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I438" t="b">
+        <v>1</v>
+      </c>
+      <c r="J438" t="n">
+        <v>1</v>
+      </c>
+      <c r="K438" t="n">
+        <v>1</v>
+      </c>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>The service was activated by a request from the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) – authorized user, and the University of Philippines – local user. Several sources suggest that the Manila NCR and lower Pampanga river basin, Philippines, has been affected by ground subsidence phenomena impacting settlements and increasing flood risk.
+The EMS service aims to provide evidence of ground moti Ground Deformation – Overview key map</t>
         </is>
       </c>
     </row>
@@ -24743,7 +24985,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard has been activated for a retrospective assessment of two floods waves registered in the upper reaches of two rivers, Nidder and Seemenbach, located in the North-East Frankfurt (Germany), in the time period from the 27thJanuary 2021 to the 11thFebruary 2021. Moreover, in the lower reaches the analysis was requested from the 11thFebruary 2021 to the 17th/18thFebruary 2021. The inundation was caused by a heavy thaw set at altitudes above 1500 meters, which, toget P04-Flood Delineation P06-Temporal analyses of occurred flood events P06-Temporal analyses of occurred flood events Mapbook - P06/P14</t>
+          <t>The CEMS Risk and Recovery Standard has been activated for a retrospective assessment of two floods waves registered in the upper reaches of two rivers, Nidder and Seemenbach, located in the North-East Frankfurt (Germany), in the time period from the 27thJanuary 2021 to the 11thFebruary 2021. Moreover, in the lower reaches the analysis was requested from the 11thFebruary 2021 to the 17th/18thFebruary 2021. The inundation was caused by a heavy thaw set at altitudes above 1500 meters, which, toget Mapbook Temporal analyses of occurred flood events Temporal analyses of occurred flood events Flood Delineation</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25282,7 @@
       <c r="L444" t="inlineStr"/>
       <c r="M444" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard has been activated by the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Bezirksregierung Münster, for a retrospective assessment of the maximum flood extent and flood depth registered during the event occurred at theEms river(Münster city, Germany) in February 2021, whose flood peak was observed on the 19th February 2021. The inundation was caused by a significant increase of temperatures to approximately 30 degrees that was reg P04-Flood Delineation 01 P04-Flood Delineation 02 P04-Flood Delineation 03 P06-Temporal analyses of occurred flood events P06-Temporal analyses of occurred flood events - Max Flood Extent</t>
+          <t>The CEMS Risk and Recovery Standard has been activated by the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Bezirksregierung Münster, for a retrospective assessment of the maximum flood extent and flood depth registered during the event occurred at theEms river(Münster city, Germany) in February 2021, whose flood peak was observed on the 19th February 2021. The inundation was caused by a significant increase of temperatures to approximately 30 degrees that was reg Temporal analyses of occurred flood events Flood Delineation 03 Flood Delineation 02 Flood Delineation 01 Temporal analyses of occurred flood events - Max Flood Extent</t>
         </is>
       </c>
     </row>
@@ -25215,7 +25457,7 @@
       <c r="L447" t="inlineStr"/>
       <c r="M447" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard service has been activated to support the assessment of the wildfire events that have affected the Piedmont region, in Italy, between the 14th and the 18th March 2021. The analysed wildfires affected some mountain areas and, fed by strong winds, destroyed about 300 hectares of forests in several municipalities. Reports by local authorities indicated serious damages to biodiversity, soil quality and to the normal ecologic functions in burned areas. The goal of  P07-Wildfire delineation and grading P07-Wildfire delineation and grading P16-Post-disaster soil erosion risk assessment P16-Post-disaster soil erosion risk assessment P16-Post-disaster soil erosion risk assessment P07-Wildfire delineation and grading P16-Post-disaster soil erosion risk assessment P16-Post-disaster soil erosion risk assessment P17-Landslide risk assessment P17-Landslide risk assessment</t>
+          <t>The CEMS Risk and Recovery Standard service has been activated to support the assessment of the wildfire events that have affected the Piedmont region, in Italy, between the 14th and the 18th March 2021. The analysed wildfires affected some mountain areas and, fed by strong winds, destroyed about 300 hectares of forests in several municipalities. Reports by local authorities indicated serious damages to biodiversity, soil quality and to the normal ecologic functions in burned areas. The goal of  Land Use and Land Cover: CLC update @1:25000 Land Use and Land Cover: CLC update @1:25000 Land Use and Land Cover: CLC update @1:25000 Land Use and Land Cover: CLC update @1:25000 Land Use and Land Cover: CLC update @1:25000 Landslide risk assessment Landslide risk assessment Landslide risk assessment Landslide risk assessment Landslide risk assessment</t>
         </is>
       </c>
     </row>
@@ -25451,7 +25693,7 @@
       <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr">
         <is>
-          <t>The explosion of a large amount of ammonium nitrate stored in a warehouse in the port of Beirut on the 4th of August 2020, had a devastating outcome not only for the port area but affecting larger areas of Greater Beirut, reaching kilometres inland. The Reform, Recovery and Reconstruction Framework (3RF) has been developed by the World Bank Group, United Nations and European Union, bringing together the civil society, the government and the international community in order to provide a roadmap t Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 (Detail, Tile 13) Reconstruction Monitoring July 2022 (Detail, Tile 12) Reconstruction Monitoring July 2022 (Detail, Tile 11) Reconstruction Monitoring July 2022 (Detail, Tile 10) Reconstruction Monitoring July 2022 (Detail, Tile 09) Reconstruction Monitoring July 2022 (Detail, Tile 08) Reconstruction Monitoring July 2022 (Detail, Tile 07) Reconstruction Monitoring July 2022 (Detail, Tile 06) Reconstruction Monitoring July 2022 (Detail, Tile 05)</t>
+          <t>The explosion of a large amount of ammonium nitrate stored in a warehouse in the port of Beirut on the 4th of August 2020, had a devastating outcome not only for the port area but affecting larger areas of Greater Beirut, reaching kilometres inland. The Reform, Recovery and Reconstruction Framework (3RF) has been developed by the World Bank Group, United Nations and European Union, bringing together the civil society, the government and the international community in order to provide a roadmap t Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022 Reconstruction Monitoring July 2022</t>
         </is>
       </c>
     </row>
@@ -25627,7 +25869,7 @@
       <c r="L454" t="inlineStr"/>
       <c r="M454" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard has been activated to support emergency operations or recovery after a major natural disaster such as flooding or tropical cyclones in Mozambique. To this scope, it has been requested to assess the effects of the Eloise Tropical cyclone that hit Mozambique starting from the second part of January 2021. Two areas of interest (AOIs) in Mozambique have been analysed. The AOIs are focused on the Pungwe River, in particular on its mouth where is present also the im P04-Flood Delineation 01 P04-Flood Delineation 02 P04-Flood Delineation 03</t>
+          <t>The CEMS Risk and Recovery Standard has been activated to support emergency operations or recovery after a major natural disaster such as flooding or tropical cyclones in Mozambique. To this scope, it has been requested to assess the effects of the Eloise Tropical cyclone that hit Mozambique starting from the second part of January 2021. Two areas of interest (AOIs) in Mozambique have been analysed. The AOIs are focused on the Pungwe River, in particular on its mouth where is present also the im Flood Delineation 02 Flood Delineation 01 Flood Delineation 03</t>
         </is>
       </c>
     </row>
@@ -25986,7 +26228,7 @@
       <c r="M460" t="inlineStr">
         <is>
           <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated to support the risk assessment analysis related to the effusive eruption of the La Soufriere volcano, in St. Vincent and the Grenadines, that started on 27thDecember 2020 and that ended up into an explosive eruption on 9thApril 2021.
-The CEMS RRM STD has been triggered during the effusive phase of the volcano activity to provide a highly detailed post-event DSM to be possibly used to simulate the lava flow pathways, analysing the  P01.2-DSM (based on radar VHR data)</t>
+The CEMS RRM STD has been triggered during the effusive phase of the volcano activity to provide a highly detailed post-event DSM to be possibly used to simulate the lava flow pathways, analysing the  DSM (based on radar VHR data)</t>
         </is>
       </c>
     </row>
@@ -26450,7 +26692,8 @@
       <c r="L468" t="inlineStr"/>
       <c r="M468" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard has been activated to assess the effects of Eta and Iota hurricanes that hit Central America starting from the beginning of November 2020. Two areas of interest (AOIs) in Honduras have been analysed. In AOI01-La Lima, located in the Ulua basin, Eta triggered large scale historic level floods, and Iota struck the region with even more intense weather that worsened conditions. The objective of this activation is to get a temporal analysis of the flood events, an P03.5-Land Use and Land Cover: CLC New @1:25000 P03.5-Land Use and Land Cover: CLC New @1:25000 P17-Landslide risk assessment P06 - Flood temporal evolution (IOTA) P06 - Maximum water depth (IOTA) P06 - Flood temporal evolution (ETA) P06 - Maximum water depth (ETA) P04-Flood Delineation</t>
+          <t>The CEMS Risk and Recovery Standard has been activated to assess the effects of Eta and Iota hurricanes that hit Central America starting from the beginning of November 2020. Two areas of interest (AOIs) in Honduras have been analysed. In AOI01-La Lima, located in the Ulua basin, Eta triggered large scale historic level floods, and Iota struck the region with even more intense weather that worsened conditions. 
+The objective of this activation is to get a temporal analysis of the flood events Land Use and Land Cover: CLC New @1:25000 Land Use and Land Cover: CLC New @1:25000 Landslide risk assessment Flood temporal evolution (IOTA) Maximum water depth (IOTA) Flood temporal evolution (ETA) Maximum water depth (ETA) Flood Delineation</t>
         </is>
       </c>
     </row>
@@ -27754,8 +27997,7 @@
       <c r="M491" t="inlineStr">
         <is>
           <t>The CEMS Risk and Recovery Standard has been activated by the Directorate-General for European Civil Protection and Humanitarian Aid Operations - European Emergency Response Coordination Centre (DG-ECHO ERCC), on behalf the ECHO field/Cameroon, following the flood occurred in Cameroon Far North Region around the 15thof September 2020.
-[Image: EMSN082_STD_PictureLocalMedia.jpg]
-The aim of the activation was to localize the areas most impacted by the inundations; this objective has been achieved P04 – Flood delineation P04 – Flood delineation P04 – Flood delineation P04 – Flood delineation P04 – Flood delineation P04 – Flood delineation P04 – Flood delineation P04 – Flood delineation P04 – Flood delineation</t>
+The aim of the activation was to localize the areas most impacted by the inundations; this objective has been achieved via the generation of a series of P04 Flood Flood delineation Flood delineation Flood delineation Flood delineation Flood delineation Flood delineation Flood delineation Flood delineation Flood delineation</t>
         </is>
       </c>
     </row>
@@ -28493,7 +28735,7 @@
       <c r="M504" t="inlineStr">
         <is>
           <t>The CEMS Risk and Recovery Standard has been activated by the Directorate-General for European Civil Protection and Humanitarian Aid Operations - European Emergency Response Coordination Centre (DG-ECHO ERCC), following the explosions occurred in Beirut, Lebanon’s capital, on the 4th of August 2020. This activation aims to provide a detailed damage assessment, delivering a picture of the spatial extent and severity of the damages.
-With that purpose, this activation includes the following Standa P08.1 – Detailed damage assessment over affected areas P13 – Ready to print maps and map books for field campaign</t>
+With that purpose, this activation includes the following Standa Detailed damage assessment over affected areas Ready to print maps and map books for field campaign</t>
         </is>
       </c>
     </row>
@@ -28889,7 +29131,7 @@
       <c r="L511" t="inlineStr"/>
       <c r="M511" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard has been activated by the Directorate-General for European Civil Protection and Humanitarian Aid Operations - European Emergency Response Coordination Centre (DG-ECHO ERCC), on behalf of the International Committee of the Red Cross (ICRC), which operates in Benghazi, Libya, to get an update of the products delivered in 2017 in the framework of a past CEMS activation (Satellite based conflict damage assessment of two selected cities in Libya available at:https: P13 – Map book P11 – Human footprint (2019-2020) P11 – Human footprint (2018-2019) P11 – Human footprint (2017-2018) P11 – Human footprint (2016-2017) P10 – Urban sprawl (2019-2020) P10 – Urban sprawl (2018-2019) P10 – Urban sprawl (2017-2018) P18 – Human settlement mapping P18 – Human settlement mapping</t>
+          <t>The CEMS Risk and Recovery Standard has been activated by the Directorate-General for European Civil Protection and Humanitarian Aid Operations - European Emergency Response Coordination Centre (DG-ECHO ERCC), on behalf of the International Committee of the Red Cross (ICRC), which operates in Benghazi, Libya, to get an update of the products delivered in 2017 in the framework of a past CEMS activation (Satellite based conflict damage assessment of two selected cities in Libya available at:https: Map book Human footprint (2019-2020) Human footprint (2018-2019) Human footprint (2017-2018) Human footprint (2016-2017) Urban sprawl (2019-2020) Urban sprawl (2018-2019) Urban sprawl (2017-2018) Human settlement mapping Human settlement mapping</t>
         </is>
       </c>
     </row>
@@ -29070,10 +29312,8 @@
           <t>The CEMS Risk and Recovery Standard has been activated to assess the damage occurred as a consequence of unprecedented frequent wildfire occurred in south and southwestern part of Iran which took place since the end of May and until June 2020.
 The Standard products that were produced to estimate the wildfires impact are:
 P03.5 - LULC: CLC @1:25000
-[Image: EMSN079_STD_AOI01_P035LULC_Map_v01.jpg]
-[Image: EMSN079_STD_AOI02_P035LULC_Map_v01.jpg]
-[Image: EMSN079_STD_AOI03_P035LULC_Map_v01.jpg]
- P07- Wildfire delineation and grading P07- Wildfire delineation and grading P07- Wildfire delineation and grading P03.5 – Land Use and Land Cover: CLC New @1:25000 P03.5 – Land Use and Land Cover: CLC New @1:25000 P03.5 – Land Use and Land Cover: CLC New @1:25000</t>
+P03.5 - LULC: CLC @1:25000 (NEW) – MMU: 0.25ha. Left: AOI01-Andika ; Middle: AOI02-Behbahan; Right: AOI03-Farashband
+P07- Wildfire delineation and Wildfire delineation and grading Wildfire delineation and grading Wildfire delineation and grading Land Use and Land Cover: CLC New @1:25000 Land Use and Land Cover: CLC New @1:25000 Land Use and Land Cover: CLC New @1:25000</t>
         </is>
       </c>
     </row>
@@ -29586,7 +29826,7 @@
       <c r="M523" t="inlineStr">
         <is>
           <t>The CEMS Risk and Recovery Standard has been activated to assess the damage occurred as a consequence of the forest fire which took place between the 20th and 27th of April 2020 in the Meinweg National Park. The Area of Interest (AOI) is located at the border region between Herkenbosch (Netherland) and Niederkrüchten (Germany).
-The post-disaster damage assessment study consists of the delineation and grading of the wildfire (P07), detailed damage assessment of the tree cover (P08.1), impact ass P07 – Wildfire delineation and grading - Monit03 P07 – Wildfire delineation and grading - Monit01 P07 – Wildfire delineation and grading P16 – Post disaster erosion risk assessment P08.1 - Detailed damage assessment analyses over affected areas P03.2 – Land Use and Land Cover: CLC Update @1:25000 P07 – Wildfire delineation and grading - Monit02</t>
+The post-disaster damage assessment study consists of the delineation and grading of the wildfire (P07), detailed damage assessment of the tree cover (P08.1), impact ass Wildfire delineation and grading Wildfire delineation and grading Wildfire delineation and grading Post disaster erosion risk assessment Detailed damage assessment analyses over affected areas Land Use and Land Cover: CLC Update @1:25000 Wildfire delineation and grading</t>
         </is>
       </c>
     </row>
@@ -29868,7 +30108,7 @@
       <c r="M528" t="inlineStr">
         <is>
           <t>The current activation addressed the forest fire that took place on 6 August 2015, in the municipality of Acebo, Cceres, Spain, and burned approximately 8,160 ha of pine trees and shrub land. It aims to evaluate the recovery of forests in terms of reduced soil erosion and the recovery of the flora.
-The RRM products calculate and compare the situation just before the event (2014 and 2015), after the event (2015 post and 2016), after the restoration activities finished (2016), and annually after  Landslide susceptibility map (Overview A1) Erosion susceptibility map (Overview A1) Assessment of biodiversity recovery (Overview A1) Assessment of vegetation recovery (Overview A1) Assessment of ground deformation (Overview A1) Assessment of ground deformation 2018-2019 with conservation measure (Overview A1) Assessment of ground deformation 2016-2017 with conservation measure (Overview A1) Assessment of observed soil loss 2014-2015 (Overview A1)</t>
+The RRM products calculate and compare the situation just before the event (2014 and 2015), after the event (2015 post and 2016), after the restoration activities finished (2016), and annually after  Landslide susceptibility map Erosion susceptibility map Assessment of biodiversity recovery Assessment of vegetation recovery Assessment of ground deformation Assessment of ground deformation 2018-2019 with conservation measure Assessment of ground deformation 2016-2017 with conservation measure Assessment of observed soil loss 2014-2015</t>
         </is>
       </c>
     </row>
@@ -29932,27 +30172,27 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>EMSN066</t>
+          <t>EMSN071</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Iran'}]</t>
+          <t>[{'short_name': 'Germany'}]</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Flood delineation and flood damage assessment, Iran</t>
+          <t>Wildfires, Preparedness, Arnsberg, Germany</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>POINT (58.96228 25.99307)</t>
+          <t>POINT (8.021859999999998 51.41891999999999)</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -29960,52 +30200,61 @@
           <t>2020-04-09T01:00:00</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr"/>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>2026-01-20T09:58:16.184451</t>
+        </is>
+      </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>recovery</t>
+          <t>preparedness</t>
         </is>
       </c>
       <c r="I530" t="b">
         <v>1</v>
       </c>
       <c r="J530" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K530" t="n">
-        <v>11</v>
-      </c>
-      <c r="L530" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could...</t>
+        </is>
+      </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t>The scope of the service request EMSN-066 is to delineate the extent and assess damage of 9 to 11 January 2020 flood event, in South-East Iran. As predicted by Copernicus EMS service GloFAS, days of heavy rain from 9 to 11 January 2020 caused severe flooding in southern Iran, in Sistan and Baluchestan, Hormozgan and south of Kerman provinces. Flooding has blocked roads and damaged houses, bridges, crops and infrastructure. Dozens of areas have been left isolated after roads were damaged or block Reservoir and dam change detection (Overview A3) Reference map (Overview A3) Flood delineation (Overview A3) Damage assessment (Overview A3) Reference map (Overview A2) Flood delineation (Overview A2) Damage assessment (Overview A2) Reservoir and dam change detection (Overview A1) Reference map (Overview A1) Flood delineation (Overview A1)</t>
+          <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could hit this territory.
+More than 63% of the town’s area is covered by forest, including several large protected areas; forest plays an important economic role in both tourism and the timber-processing busi Reference map Land Use Land Cover map Pre-disaster forest fire hazard Pre-disaster forest fire exposure</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>EMSN071</t>
+          <t>EMSN066</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Germany'}]</t>
+          <t>[{'short_name': 'Iran'}]</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Wildfires, Preparedness, Arnsberg, Germany</t>
+          <t>Flood delineation and flood damage assessment, Iran</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>POINT (8.021859999999998 51.41891999999999)</t>
+          <t>POINT (58.96228 25.99307)</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -30013,34 +30262,25 @@
           <t>2020-04-09T01:00:00</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>2026-01-20T09:58:16.184451</t>
-        </is>
-      </c>
+      <c r="G531" t="inlineStr"/>
       <c r="H531" t="inlineStr">
         <is>
-          <t>preparedness</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I531" t="b">
         <v>1</v>
       </c>
       <c r="J531" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K531" t="n">
-        <v>4</v>
-      </c>
-      <c r="L531" t="inlineStr">
-        <is>
-          <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could...</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="L531" t="inlineStr"/>
       <c r="M531" t="inlineStr">
         <is>
-          <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could hit this territory.
-More than 63% of the town’s area is covered by forest, including several large protected areas; forest plays an important economic role in both tourism and the timber-processing busi Reference map (Overview A1) Land Use Land Cover map (Overview A1) Pre-disaster forest fire hazard (Overview A1) Pre-disaster forest fire exposure (Overview A1)</t>
+          <t>The scope of the service request EMSN-066 is to delineate the extent and assess damage of 9 to 11 January 2020 flood event, in South-East Iran. As predicted by Copernicus EMS service GloFAS, days of heavy rain from 9 to 11 January 2020 caused severe flooding in southern Iran, in Sistan and Baluchestan, Hormozgan and south of Kerman provinces. Flooding has blocked roads and damaged houses, bridges, crops and infrastructure. Dozens of areas have been left isolated after roads were damaged or block Reference map Reservoir and dam change detection Flood delineation Damage assessment Reference map Flood delineation Damage assessment Reservoir and dam change detection Reference map Flood delineation</t>
         </is>
       </c>
     </row>
@@ -30205,7 +30445,7 @@
       <c r="M534" t="inlineStr">
         <is>
           <t>CEMS Risk and Recovery Standard was activated on behalf of the City of Zagreb (Office of Emergency Management) with the objective of assessing damages related to the earthquake that hit the area of Zagreb (Croatia) on the 22 March 2020. Preliminary reports and information coming from the area indicated heavily damaged roofs and assets in the City centre.
-The products generated in the framework of this activation aim to provide an updated reference dataset over the city of Zagreb, a detailed dam P09 - Reconstruction monitoring P08.1 - Detailed damage assessment analyses over affected areas P02.1 - Reference dataset</t>
+The products generated in the framework of this activation aim to provide an updated reference dataset over the city of Zagreb, a detailed dam Reconstruction monitoring Detailed damage assessment analyses over affected areas Reference dataset</t>
         </is>
       </c>
     </row>
@@ -30258,7 +30498,7 @@
       <c r="L535" t="inlineStr"/>
       <c r="M535" t="inlineStr">
         <is>
-          <t>EMSN-065 was activated to support and assist monitoring recovery after the passage of the Category 5 Hurricane Matthew on the 4th of October 2016, over seven selected areas, by analysing environmental aspects such as agriculture activities and forest over protected areas. The geographical focus of this work is the Western area of the Grand’Anse, Haiti, a very badly affected sector. The aim was to build a comprehensive database to support recovery aid organizations in recovery monitoring of the c Agricultural status change post-event Agricultural status change post-event Agricultural status change post-event Agricultural status change post-event Agricultural status change post-event Agricultural status post-event (2019) Agricultural status post-event (2019) Agricultural status post-event (2019) Agricultural status post-event (2019) Agricultural status post-event (2019)</t>
+          <t>EMSN-065 was activated to support and assist monitoring recovery after the passage of the Category 5 Hurricane Matthew on the 4th of October 2016, over seven selected areas, by analysing environmental aspects such as agriculture activities and forest over protected areas. The geographical focus of this work is the Western area of the Grand’Anse, Haiti, a very badly affected sector. The aim was to build a comprehensive database to support recovery aid organizations in recovery monitoring of the c Agricultural status change pre/post-event Agricultural status post-event Agricultural status change post-event Agricultural status change post-event Agricultural status change post-event Agricultural status change post-event Agricultural status change post-event Agricultural status post-event (2019) Agricultural status post-event (2019) Agricultural status post-event (2019)</t>
         </is>
       </c>
     </row>
@@ -30312,7 +30552,7 @@
       <c r="M536" t="inlineStr">
         <is>
           <t>Between 22 and 23 January 2020, the Mediterranean storm "Gloria" hit Southern France. Possible effects and damages were flooding, damage to forest, soil instability, resulting in an increasing risk of landslides and soil erosion. The scope of the service request was to evaluate forest damage and its extent and to analyse the increase of soil erosion and landslide risk; to this end, three products were designed and generated.
-Thesoil erosion riskassessment was conducted based on a soil erodibili Land Use and Land Cover Damage assessment on wooden areas Damage assessment on wooden areas (Detail, Tile 14) Damage assessment on wooden areas (Detail, Tile 13) Damage assessment on wooden areas (Detail, Tile 12) Damage assessment on wooden areas (Detail, Tile 11) Damage assessment on wooden areas (Detail, Tile 10) Damage assessment on wooden areas (Detail, Tile 09) Damage assessment on wooden areas (Detail, Tile 08) Damage assessment on wooden areas (Detail, Tile 07)</t>
+Thesoil erosion riskassessment was conducted based on a soil erodibili Land Use and Land Cover Damage assessment on wooden areas Damage assessment on wooden areas Damage assessment on wooden areas Damage assessment on wooden areas Damage assessment on wooden areas Damage assessment on wooden areas Damage assessment on wooden areas Damage assessment on wooden areas Damage assessment on wooden areas</t>
         </is>
       </c>
     </row>
@@ -30651,7 +30891,7 @@
       <c r="M542" t="inlineStr">
         <is>
           <t>The CEMS Risk and Recovery Standard has been activated on behalf of the Ministry of Environment of the state of Brandenburg with the objective of assessing a flood event casued by heavy rainfall that hit the area of Rhin-Havelluch, District Oberhavel in Brandenburg (Germany) in June 2017. The peak of the precipitations occurred between the 29th and 30th June 2017. However, rainy days occurred during the next weeks, leading to the permanence of flooded areas until August 2017.
-The products gener P06 - Temporal analyses of occurred flood events. Maximum flood retention P06 - Temporal analyses of occurred flood events. Maximum flood retention P06 - Temporal analyses of occurred flood events. Maximum flood extent and maximum flood depth P06 - Temporal analyses of occurred flood events. Maximum flood extent and maximum flood depth P04 - Flood Delineation (10.07.2017-15.08.2017) P04 - Flood Delineation (10.07.2017-15.08.2017) P04 - Flood Delineation (30.06.2017-04.07.2017) P04 - Flood Delineation (30.06.2017-04.07.2017) P08.2 Detailed damage assessment analyses over affected areas P08.2 Detailed damage assessment analyses over affected areas</t>
+The products gener Temporal analyses of occurred flood events. Maximum flood retention Temporal analyses of occurred flood events. Maximum flood retention Temporal analyses of occurred flood events. Maximum flood extent and maximum flood depth Temporal analyses of occurred flood events. Maximum flood extent and maximum flood depth Flood Delineation (10.07.2017-15.08.2017) Flood Delineation (10.07.2017-15.08.2017) Flood Delineation (30.06.2017-04.07.2017) Flood Delineation (30.06.2017-04.07.2017) Detailed damage assessment analyses over affected areas Detailed damage assessment analyses over affected areas</t>
         </is>
       </c>
     </row>
@@ -30710,35 +30950,35 @@
         <is>
           <t>This activation follows a windstorm occurred in the Gorenjska Region, Slovenia, which caused severe damages to the woods in the area surrounding the airport of Ljubljana. The event hit the area twice: on the 5th and 6th of February 2020, and few days later, on the 10th and 11th of February 2020. The Authorized User requested the damage assessment of woods within the area of interest.
 Proposed solution and results
-[Image: EMSN070_STD_PostEventDSMZoom1_19032020.png]
-Figure 1 - Detail of the pos P08.1 - Detailed damage assessment analyses over affected areas P01.1 - DSM (based on optical VHR data) P15 - Detailed impact assessment analyses on selected aspect</t>
+Figure 1 - Detail of the post-event DSM
+Figure 2 - Affected areas per damage gra Detailed damage assessment analyses over affected areas DSM (based on optical VHR data) Detailed impact assessment analyses on selected aspect</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>EMSN064</t>
+          <t>EMSN063</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Ukraine'}]</t>
+          <t>[{'short_name': 'Nigeria'}]</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
+          <t>Crop change detection in conflict areas, Nigeria</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>POINT (23.87015 47.95273)</t>
+          <t>POINT (12.36791 13.49555)</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -30756,77 +30996,77 @@
         <v>1</v>
       </c>
       <c r="J544" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K544" t="n">
+        <v>5</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
+The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>EMSN064</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Ukraine'}]</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>POINT (23.87015 47.95273)</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2020-02-14T01:00:00</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I545" t="b">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
+        <v>1</v>
+      </c>
+      <c r="K545" t="n">
         <v>4</v>
       </c>
-      <c r="L544" t="inlineStr"/>
-      <c r="M544" t="inlineStr">
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr">
         <is>
           <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
 The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>EMSN063</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Nigeria'}]</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Crop change detection in conflict areas, Nigeria</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>POINT (12.36791 13.49555)</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>2020-02-14T01:00:00</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I545" t="b">
-        <v>1</v>
-      </c>
-      <c r="J545" t="n">
-        <v>5</v>
-      </c>
-      <c r="K545" t="n">
-        <v>5</v>
-      </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
-        </is>
-      </c>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
-The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
-        </is>
-      </c>
-    </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
@@ -30934,7 +31174,7 @@
       <c r="M547" t="inlineStr">
         <is>
           <t>This is an exceptional activation of the Risk and Recovery Mapping Service as the analysis does not represent the actual risk assessment, but has been defined by the needs of an exercise planned on 1 April 2020 by the fire-brigade and civil protection command team of the German city of Herne.
-The simulated scenario consists of a flooding event occurred in Herne due to high water levels of the Emscher river, caused by heavy rainfall over the German cities of Dortmund and Castrop-Rauxel. The sout P05 - Modelled flood extent for major events</t>
+The simulated scenario consists of a flooding event occurred in Herne due to high water levels of the Emscher river, caused by heavy rainfall over the German cities of Dortmund and Castrop-Rauxel. The sout Modelled flood extent for major events</t>
         </is>
       </c>
     </row>
@@ -30987,7 +31227,7 @@
       <c r="L548" t="inlineStr"/>
       <c r="M548" t="inlineStr">
         <is>
-          <t>Heavy rains from the 9thto the 11thof January 2020 led to flash floods in south-east Iran (figure 1), where heavy damages on infrastructures, buildings and croplands have been reported. The CEMS Risk and Recovery Mapping service has been activated on the 31stof January. The aim of this activation is to detect flooded areas around two cities, i.e. Minab and Seerik, in order to help assessing the impact of the disaster and managing the aftermath in terms of planning and budget, as well as to use t P04 - Flood Delineation P04 - Flood Delineation</t>
+          <t>Heavy rains from the 9thto the 11thof January 2020 led to flash floods in south-east Iran (figure 1), where heavy damages on infrastructures, buildings and croplands have been reported. The CEMS Risk and Recovery Mapping service has been activated on the 31stof January. The aim of this activation is to detect flooded areas around two cities, i.e. Minab and Seerik, in order to help assessing the impact of the disaster and managing the aftermath in terms of planning and budget, as well as to use t Flood Delineation Flood Delineation</t>
         </is>
       </c>
     </row>
@@ -32816,7 +33056,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>EMSR389</t>
+          <t>EMSR390</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -32831,12 +33071,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Forest fire in Loutraki area- Greece</t>
+          <t>Forest fire in Zakynthos Island- Greece</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>POINT (22.973 37.997)</t>
+          <t>POINT (20.806 37.698)</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -32846,7 +33086,7 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>2019-09-20T13:40:00</t>
+          <t>2019-09-25T11:41:00</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -32863,13 +33103,17 @@
       <c r="K581" t="n">
         <v>2</v>
       </c>
-      <c r="L581" t="inlineStr"/>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>A forest fire,  broke out in 15-09-2019 near Lithakia village in Zakynthos Island, 250 Km West from Athens. Fanned by strong winds, this fire forced the evacuation of the villages of Keri and Agalas as a precaution. Copernicus EMS Mapping products will be used for damage assessment, recovery and...</t>
+        </is>
+      </c>
       <c r="M581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>EMSR390</t>
+          <t>EMSR389</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -32884,12 +33128,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Forest fire in Zakynthos Island- Greece</t>
+          <t>Forest fire in Loutraki area- Greece</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>POINT (20.806 37.698)</t>
+          <t>POINT (22.973 37.997)</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -32899,7 +33143,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>2019-09-25T11:41:00</t>
+          <t>2019-09-20T13:40:00</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -32916,11 +33160,7 @@
       <c r="K582" t="n">
         <v>2</v>
       </c>
-      <c r="L582" t="inlineStr">
-        <is>
-          <t>A forest fire,  broke out in 15-09-2019 near Lithakia village in Zakynthos Island, 250 Km West from Athens. Fanned by strong winds, this fire forced the evacuation of the villages of Keri and Agalas as a precaution. Copernicus EMS Mapping products will be used for damage assessment, recovery and...</t>
-        </is>
-      </c>
+      <c r="L582" t="inlineStr"/>
       <c r="M582" t="inlineStr"/>
     </row>
     <row r="583">
@@ -33718,8 +33958,8 @@
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>The specific activation focuses on deepening the analysis concerning the occurrence of floods within a transboundary AOI that corresponds to the Drin catchment area and more specifically to the part that extends into four countries, namely Albania, Kosovo*, the Former Yugoslavian Republic of Macedonia and Montenegro.
-The service and the products aim to serve the scope of the Drin River Cooperation agreement on sustainable management of water resources in the Drin catchment area through providi Reference Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 10/1992 (Bar, Cetinje, Podgorica, Shkodra, Ulcinj) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 08/1995 (Bar, Cetinje, Lezhe, Podgorica, Shkodra, Ulcinj) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Economic Assets map - Critical Infrastructures Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 10/2002 (Bar, Lezhe, Podgorica, Shkodra, Ulcinj) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 12/2004 (Bar, Cetinje, Danilovgrad, Niksic, Podgorica, Shkodra) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment (Drin Basin (11-2007)) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 12/2009 - 01/2010 (Basin Area) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 11,12/2010 (Bar, Cetinje, Lezhe, Podgorica, Shkodra, Ulcinj) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 03,04/2013 (Basin Area) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact</t>
+          <t>The specific activation focuses on deepening the analysis concerning the occurrence of floods within a transboundary AOI that corresponds to the Drin catchment area and more specifically to the part that extends into four countries, namely Albania, Kosovo, the Former Yugoslavian Republic of Macedonia and Montenegro.
+The service and the products aim to serve the scope of the Drin River Cooperation agreement on sustainable management of water resources in the Drin catchment area through providi Reference Map Historical Analysis - Maximum Flood Extent and Damages Assessment, 10/1992 (Bar, Cetinje, Podgorica, Shkodra, Ulcinj) Map Historical Analysis - Maximum Flood Extent and Damages Assessment, 08/1995 (Bar, Cetinje, Lezhe, Podgorica, Shkodra, Ulcinj) Map Historical Analysis - Maximum Flood Extent and Damages Assessment, 10/2002 (Bar, Lezhe, Podgorica, Shkodra, Ulcinj) Map Historical Analysis - Maximum Flood Extent and Damages Assessment, 12/2004 (Bar, Cetinje, Danilovgrad, Niksic, Podgorica, Shkodra) Map Historical Analysis - Maximum Flood Extent and Damages Assessment (Drin Basin (11-2007)) Map Historical Analysis - Maximum Flood Extent and Damages Assessment, 12/2009 - 01/2010 (Basin Area) Map Historical Analysis - Maximum Flood Extent and Damages Assessment, 11,12/2010 (Bar, Cetinje, Lezhe, Podgorica, Shkodra, Ulcinj) Map Historical Analysis - Maximum Flood Extent and Damages Assessment, 03,04/2013 (Basin Area) Map Historical Analysis - Maximum Flood Extent and Damages Assessment, 11/2014 (Basin Area) Map</t>
         </is>
       </c>
     </row>
@@ -34249,10 +34489,8 @@
       <c r="L607" t="inlineStr"/>
       <c r="M607" t="inlineStr">
         <is>
-          <t>[Image: 11_11_15.png]
-The scope of the service request EMSN060 is to evaluate the status of the environment affected by two forest fires that occurred in the summer of 2017 in the Spanish provinces of Huelva and Seville (Andalusia Region). To allow detailed analyses, the affected areas (4,163 ha in AOI 01-Granada de Rio Tinto and 823 ha in AOI 02-El Campillo) were flown to get recent aerial orthoimages (GSD 0.2m, RGB and NIR bands) one year after the event.
-[Image: 11_15_59.png]
-Assesse Reference Cartography (Overview A2) Reference Cartography (Overview A1) Product 6-2: Landslide Risk (Overview A2) Product 6-2: Landslide Risk (Overview A1) Product 6-1: Erosion Risk (Overview A2) Product 6-1: Erosion Risk (Overview A1) Product 5: Assessment of the road network status  (Overview A2) Product 5: Assessment of the road network status  (Overview A1) Product 4: Assessment of the observed soil loss (Overview A2) Product 4: Assessment of the observed soil loss (Overview A1)</t>
+          <t>The scope of the service request EMSN060 is to evaluate the status of the environment affected by two forest fires that occurred in the summer of 2017 in the Spanish provinces of Huelva and Seville (Andalusia Region). To allow detailed analyses, the affected areas (4,163 ha in AOI 01-Granada de Rio Tinto and 823 ha in AOI 02-El Campillo) were flown to get recent aerial orthoimages (GSD 0.2m, RGB and NIR bands) one year after the event.
+Assessed by the spectral indices: Normalized Burn Rat Reference Cartography Reference Cartography Landslide Risk Landslide Risk Erosion Risk Erosion Risk Assessment of the road network status Assessment of the road network status Assessment of the observed soil loss Assessment of the observed soil loss</t>
         </is>
       </c>
     </row>
@@ -34571,8 +34809,7 @@
       <c r="M613" t="inlineStr">
         <is>
           <t>The scope of the service request was to carry out a pre‐disaster Forest Fire Risk assessment in two areas near Split and Dubrovnik in Croatia. Apart from the General Reference context the following Risk and Recovery products were generated:
-[Image: 15_22_30.png]
-The assessment of the forest firehazardaccounts for fire intensity and surface properties. The generation of a forest fire index layer was based on specific assumptions and accounts for anaglyph, aspect &amp; height zones, vegetation c Population, Assets and Transportation Network at Risk - Low Season Map - Forest Fire Risk Assessment Land Use and Land Cover Map - Forest Fire Risk Assessment Population, Assets and Transportation Network at Risk - Low Season Map - Forest Fire Risk Assessment Population, Assets and Transportation Network at Risk - Low Season Map - Forest Fire Risk Assessment Population, Assets and Transportation Network at Risk - Low Season Map - Forest Fire Risk Assessment Population, Assets and Transportation Network at Risk - Low Season Map - Forest Fire Risk Assessment Population, Assets and Transportation Network at Risk - Low Season Map - Forest Fire Risk Assessment Population, Assets and Transportation Network at Risk - Low Season Map - Forest Fire Risk Assessment Population, Assets and Transportation Network at Risk - Low Season Map - Forest Fire Risk Assessment Population, Assets and Transportation Network at Risk - High Season Map - Forest Fire Risk Assessment</t>
+The assessment of the forest firehazardaccounts for fire intensity and surface properties. The generation of a forest fire index layer was based on specific assumptions and accounts for anaglyph, aspect &amp; height zones, vegetation cover, climatological  Population, Assets and Transportation Network at Risk - Low Season Map Population, Assets and Transportation Network at Risk - Low Season Map Population, Assets and Transportation Network at Risk - Low Season Map Population, Assets and Transportation Network at Risk - Low Season Map Population, Assets and Transportation Network at Risk - Low Season Map Population, Assets and Transportation Network at Risk - Low Season Map Reference Map Population, Assets and Transportation Network at Risk - Low Season Map Population, Assets and Transportation Network at Risk - Low Season Map Population, Assets and Transportation Network at Risk - High Season Map</t>
         </is>
       </c>
     </row>
@@ -35380,7 +35617,7 @@
       <c r="M628" t="inlineStr">
         <is>
           <t>Time series plots are available under request per each persistent scatterer (PS) point (668710 PS points) indicating ground subsidence trend.Contact us at JRC-EMS-RISKRECOVERYMAPPING@ec.europa.eu.
-The EMSN062 service provides geospatial information supporting investigations into area based changes of subsidence rates and facilitating assessment of drivers of ground subsidence in the Mekong Delta, Vietnam. Primary objective of the service is provision of spatially and temporally consistent, de Estimated average ground subsidence velocity [cm/year] (Overview A1)</t>
+The EMSN062 service provides geospatial information supporting investigations into area based changes of subsidence rates and facilitating assessment of drivers of ground subsidence in the Mekong Delta, Vietnam. Primary objective of the service is provision of spatially and temporally consistent, de Estimated average ground subsidence velocity [cm/year]</t>
         </is>
       </c>
     </row>
@@ -35960,7 +36197,7 @@
       <c r="M638" t="inlineStr">
         <is>
           <t>The specific service implementation focuses on the generation of information relating to the horizontal and vertical displacement across the AOI as a consequence of the 28th September earthquake (7.5 magnitude) that hit the island of Sulawesi, Indonesia, triggering a number of aftershocks.
-The analysis involved satellite SAR imagery (Sentinel-1) processing through an offset tracking technique. Ascending and Descending images were selected, both prior to and after the event. This allowed the g Vertical Displacement Map - Ground Deformation analyses, Sulawesi, Indonesia  E-W Displacement Map - Ground Deformation analyses, Sulawesi, Indonesia  N-S Displacement Map - Ground Deformation analyses, Sulawesi, Indonesia</t>
+The analysis involved satellite SAR imagery (Sentinel-1) processing through an offset tracking technique. Ascending and Descending images were selected, both prior to and after the event. This allowed the g Vertical Displacement Map E-W Displacement Map N-S Displacement Map</t>
         </is>
       </c>
     </row>
@@ -36014,7 +36251,7 @@
       <c r="M639" t="inlineStr">
         <is>
           <t>Since 2015, Yemen has experienced a devastating civil war, resulting, among other things, in physical damage to the building stock and infrastructures. The purpose of the requested mapping is to generate asset damage assessment information for the Aden and Sana'a cities in Yemen, as well as information on their expansion within selected reference periods.
-The analysis involved photointerpretation of VHR satellite imagery, through comparing pre-conflict (2015) and up-to-date (2018) image datas Reference map - Aden city Map - Satellite-based Conflict Damage Assessment in Yemen Land Use and Land Cover - Aden city Map - Satellite-based Conflict Damage Assessment in Yemen Reference map - Sana city Map - Satellite-based Conflict Damage Assessment in Yemen Land Use and Land Cover - Sana city Map - Satellite-based Conflict Damage Assessment in Yemen Night Lights Map - 2018: Sana and Aden cities Map - Satellite-based Conflict Damage Assessment in Yemen Night Lights Map - end of 2016: Sana and Aden cities Map - Satellite-based Conflict Damage Assessment in Yemen Night Lights Map - 2014 to 02/2015: Sana and Aden cities Map - Satellite-based Conflict Damage Assessment in Yemen Urban Sprawl - Land Resource Impact Map: Aden city  Map - Satellite-based Conflict Damage Assessment in Yemen  Urban Sprawl - Land Use / Land Cover Change Map: Sana city Map - Satellite-based Conflict Damage Assessment in Yemen Urban Sprawl - Land Use / Land Cover Change Map: Sana city Map - Satellite-based Conflict Damage Assessment in Yemen</t>
+The analysis involved photointerpretation of VHR satellite imagery, through comparing pre-conflict (2015) and up-to-date (2018) image datas Urban Sprawl - Land Resource Impact Map: Aden city Map Reference map - Aden city Map Land Use and Land Cover - Aden city Map Reference map - Sana city Map Land Use and Land Cover - Sana city Map Night Lights Map - 2018: Sana and Aden cities Map Night Lights Map - end of 2016: Sana and Aden cities Map Night Lights Map - 2014 to 02/2015: Sana and Aden cities Map Urban Sprawl - Land Use / Land Cover Change Map: Sana city Map Urban Sprawl - Land Use / Land Cover Change Map: Sana city Map</t>
         </is>
       </c>
     </row>
@@ -36295,7 +36532,7 @@
       <c r="L644" t="inlineStr"/>
       <c r="M644" t="inlineStr">
         <is>
-          <t>The EMSN057 service provides geospatial information facilitating assessment of drivers of ground subsidence and to supporting analysis of the relation between detected ground subsidence and land use changes in Ca Mau, Long Xuyen and Rach Gia areas in the Mekong delta, Vietnam. The primary objective of the service is provision of spatially and temporally consistent, dense and synoptic results giving insight on the distribution and variance of subsidence phenomena in space and its dynamics in time Product 2: Estimated Annual Subsidence Displacement Change - 2018-2017 (Overview A3) Product 2: Estimated Annual Subsidence Displacement Change - 2018-2017 (Overview A2) Product 2: Estimated Annual Subsidence Displacement Change - 2018-2017 (Overview A1) Product 2: Estimated Annual Subsidence Displacement Change - 2017-2016 (Overview A3) Product 2: Estimated Annual Subsidence Displacement Change - 2017-2016 (Overview A2) Product 2: Estimated Annual Subsidence Displacement Change - 2017-2016 (Overview A1) Product 2: Estimated Annual Subsidence Displacement Change - 2016-2015 (Overview A3) Product 2: Estimated Annual Subsidence Displacement Change - 2016-2015 (Overview A2) Product 2: Estimated Annual Subsidence Displacement Change - 2016-2015 (Overview A1) Product 2: Estimated Annual Subsidence Displacement Change - 2015-2014 (Overview A3)</t>
+          <t>The EMSN057 service provides geospatial information facilitating assessment of drivers of ground subsidence and to supporting analysis of the relation between detected ground subsidence and land use changes in Ca Mau, Long Xuyen and Rach Gia areas in the Mekong delta, Vietnam. The primary objective of the service is provision of spatially and temporally consistent, dense and synoptic results giving insight on the distribution and variance of subsidence phenomena in space and its dynamics in time Estimated Annual Subsidence Displacement Change - 2018-2017 Estimated Annual Subsidence Displacement Change - 2018-2017 Estimated Annual Subsidence Displacement Change - 2018-2017 Estimated Annual Subsidence Displacement Change - 2017-2016 Estimated Annual Subsidence Displacement Change - 2017-2016 Estimated Annual Subsidence Displacement Change - 2017-2016 Estimated Annual Subsidence Displacement Change - 2016-2015 Estimated Annual Subsidence Displacement Change - 2016-2015 Estimated Annual Subsidence Displacement Change - 2016-2015 Estimated Annual Subsidence Displacement Change - 2015-2014</t>
         </is>
       </c>
     </row>
@@ -36972,8 +37209,7 @@
       <c r="M656" t="inlineStr">
         <is>
           <t>In June 2013,  wide flooding and consequent damage and losses occurred in Central Europe, affecting especially Southern and Eastern Germany and some areas in Czech Republic, Austria and Switzerland. It was one of the largest floods in the past two centuries.
-[Image: Untitled(9).png]
-The outcome of EMSN-056 activation aims to provide further results to help in the analysis of this flood event dynamics. The current study delimits the flood extent of every available source, not analysed before, d Product 1: Observed flood extent (Overview A1) Product 1: Observed flood extent (Overview A1) Product 1: Observed flood extent (Overview A1) Product 1: Observed flood extent (Overview A1)</t>
+The outcome of EMSN-056 activation aims to provide further results to help in the analysis of this flood event dynamics. The current study delimits the flood extent of every available source, not analysed before, during more than one month  Observed flood extent Observed flood extent Observed flood extent Observed flood extent</t>
         </is>
       </c>
     </row>
@@ -38029,8 +38265,7 @@
           <t>The activation focuses on two flood disaster management levels.
 The first refers to post‐disaster situation analysis concerning the impact of intense rain (16 December 2017) over the Villa Santa Lucia, in the commune of Chaitén, Chile (CL).
 Mudflow Delineation - Damage Assessment
-[Image: 11_36_10.png]
-Comprehensive knowledge of the disaster is provided through a number of information layers, as is the spatial extent of the flood/ landslide (mudslide) caused by the rainfall, the impac Population and Environmental Elements at Risk Map - Flood Risk Mapping Assets and Transportation Network at Risk Map - Flood Risk Mapping Land Use and Land Cover Map - Flood risk mapping Land Use and Land Cover Map - Flood risk mapping Reference Map - Flood risk mapping Reference Map - Flood risk mapping Mudflow Delineation and Damage Assessment Map - Flood Risk Mapping</t>
+Comprehensive knowledge of the disaster is provided through a number of information layers, as is the spatial extent of the flood/ landslide (mudslide) caused by the rainfall, the impact on population and a Population and Environmental Elements at Risk Map Assets and Transportation Network at Risk Map Land Use and Land Cover Map Land Use and Land Cover Map Reference Map Reference Map Mudflow Delineation and Damage Assessment Map</t>
         </is>
       </c>
     </row>
@@ -38686,7 +38921,7 @@
       <c r="M685" t="inlineStr">
         <is>
           <t>Friederike storm hit several countries across Western Europe in early 2018, causing extensive damages and traffic disruption. While centred over Germany winds speed up to 200 km/h caused  severe damage across the country.
-The objective of the current activation is to provide a baseline database to perform a damage assessment on forests, after the storm Friederike in support of planning and forest management activities in Federal State of Hessen.  The Hessen is the most forested state in Germa Reference map (Overview A1) Land Cover Land Use map (Overview A1) Damage Assessment of Assets in t1 (Overview A1)</t>
+The objective of the current activation is to provide a baseline database to perform a damage assessment on forests, after the storm Friederike in support of planning and forest management activities in Federal State of Hessen.  The Hessen is the most forested state in Germa Reference map Land Cover Land Use map Damage Assessment of Assets in t1</t>
         </is>
       </c>
     </row>
@@ -39107,7 +39342,7 @@
       <c r="M692" t="inlineStr">
         <is>
           <t>Support monitoring of recovery after the passage of the Category 5 Hurricane Matthew on the 4th of October 2016. Six areas were selected to analyse several environmental aspects, including agricultural activities, forest in protected areas, mangrove areas, and finally coastline modifications. The geographical focus of this work is the Western area of the Grand’Anse, Haiti, which was severely affected.
-The aim is to build a comprehensive database to support recovery aid organizations in recovery COASTALLINEEVOLUTION(OVERVIEW) COASTALLINEDELINEATION(OVERVIEW) MANGROVEDAMAGEASSESSMENT(OVERVIEW) MANGROVEPREEVENTSITUATION(OVERVIEW) AGRICULTURALACTIVITIESCHANGE(OVERVIEW) AGRICULTURALACTIVITIESCHANGE(OVERVIEW) AGRICULTURALACTIVITIESCHANGE(OVERVIEW) AGRICULTURALACTIVITIESPOSTEVENT(OVERVIEW) AGRICULTURALACTIVITIESPOSTEVENT(OVERVIEW) AGRICULTURALACTIVITIESPOSTEVENT(OVERVIEW)</t>
+The aim is to build a comprehensive database to support recovery aid organizations in recovery Agricultural activities change Coastline evolution Coastline delineation Mangrove damage assessment Mangrove pre-event situation Agricultural activities change Agricultural activities change Agricultural activities post-event Agricultural activities post-event Agricultural activities post-event</t>
         </is>
       </c>
     </row>
@@ -39405,7 +39640,7 @@
       <c r="M697" t="inlineStr">
         <is>
           <t>The purpose of the requested mapping is to generate comprehensive knowledge through performing post-disaster situation analysis concerning hurricane Irma (September 2017) over two Caribbean islands: the French part of Saint Martin and Saint Barthélemy (FR).
-Towards the implementation of adequate recovery activities, efficient support and informed decision making of the involved stakeholders, damage assessment and monitoring of the reconstruction activities were performed. The monitoring of th Reconstruction Activity - July 2019 Map - Post IRMA Analysis Reconstruction Activity - July 2019 Map - Post IRMA Analysis Reconstruction Activity - March 2019 Map - Post IRMA Analysis Reconstruction Activity - March 2019 Map - Post IRMA Analysis Reconstruction Activity - Dec 2018 Map - Post IRMA Analysis Reconstruction Activity - Dec 2018 Map - Post IRMA Analysis Reconstruction Activity - Sep 2018 Map - Post IRMA Analysis Reconstruction Activity - Sep 2018 Map - Post IRMA Analysis Reconstruction Activity - Aug 2018 Map - Post IRMA Analysis Reconstruction Activity - Aug 2018 Map - Post IRMA Analysis</t>
+Towards the implementation of adequate recovery activities, efficient support and informed decision making of the involved stakeholders, damage assessment and monitoring of the reconstruction activities were performed. The monitoring of th Reconstruction Activity - July 2019 Map Reconstruction Activity - July 2019 Map Reconstruction Activity - March 2019 Map Reconstruction Activity - March 2019 Map Reconstruction Activity - Dec 2018 Map Reconstruction Activity - Dec 2018 Map Reconstruction Activity - Sep 2018 Map Reconstruction Activity - Sep 2018 Map Reconstruction Activity - Aug 2018 Map Reconstruction Activity - Aug 2018 Map</t>
         </is>
       </c>
     </row>
@@ -39641,7 +39876,7 @@
       <c r="L701" t="inlineStr"/>
       <c r="M701" t="inlineStr">
         <is>
-          <t>The objective of this activation is to provide a general reference content to support activities of administration in reconstruction work of damage caused by Cyclone Matthew (October 2016) over two areas of interest containing the cities of Jérémie and Les Cayes, and to understand vulnerabilities during the recovery period. The focus of EMSN-050 activation was the detection of buildings and assets of all kinds affected by the cyclone, and understanding how people temporarily had to relocate thei Reference map (Overview A1) Reference map (Overview A1) Monitoring of Reconstruction Activities of the Assets in t3 (Overview A1) Monitoring of Reconstruction Activities of the Assets in t3 (Overview A1) Land Cover Land Use map (Overview A1) Land Cover Land Use map (Overview A1) Monitoring of Evolution IDP camps  t1-t3  Map  (Overview A1) Monitoring of Evolution IDP camps  t1-t3  Map  (Overview A1) Identification of IDP camps Map in three time stages (Overview A1) Identification of IDP camps Map in three time stages (Overview A1)</t>
+          <t>The objective of this activation is to provide a general reference content to support activities of administration in reconstruction work of damage caused by Cyclone Matthew (October 2016) over two areas of interest containing the cities of Jérémie and Les Cayes, and to understand vulnerabilities during the recovery period. The focus of EMSN-050 activation was the detection of buildings and assets of all kinds affected by the cyclone, and understanding how people temporarily had to relocate thei Reference map Reference map Monitoring of Reconstruction Activities of the Assets in t3 Monitoring of Reconstruction Activities of the Assets in t3 Land Cover Land Use map Land Cover Land Use map Monitoring of Evolution IDP camps t1-t3 Map Monitoring of Evolution IDP camps t1-t3 Map Identification of IDP camps Map in three time stages Identification of IDP camps Map in three time stages</t>
         </is>
       </c>
     </row>
@@ -39703,7 +39938,7 @@
       <c r="M702" t="inlineStr">
         <is>
           <t>The purpose of the requested mapping is to generate comprehensive knowledge through performing pre-disaster situation analysis, concerning a potential eruption of the Nyiragongo volcano located near to Goma, capital of North Kivu province in the eastern Democratic Republic of the Congo (DRC).
-The results refer to background information as well as to the assessment of the impact of a potential volcano activity on the surrounding urban agglomerations and infrastructures; detailed Digital Elevat Transportation Network Vulnerability to disruption Map - Volcanic Risk Assessment  Lava Flow Hazard  Map - Volcanic Risk Assessment  Land Use and Land Cover Map - Volcanic Risk Assessment Reference Map - Volcanic Risk Assessment</t>
+The results refer to background information as well as to the assessment of the impact of a potential volcano activity on the surrounding urban agglomerations and infrastructures; detailed Digital Elevat Transportation Network Vulnerability to disruption Map Lava Flow Hazard Map Land Use and Land Cover Map Reference Map</t>
         </is>
       </c>
     </row>
@@ -40307,8 +40542,7 @@
           <t>This activation focuses on post-disaster situation analysis, concerning flood events that occurred from January 18 to January 22, 2017, within two main Sardinia’s rivers' flows (Tirso and Cedrino).
 More specifically it addresses the evaluation of flood risk and related impacts on the use of soil, structure and infrastructure.
 Flooding At Peak Conditions - Damage Assessment
-[Image: 16_45_59.png]
-Observed flood extent mapping was estimated using the available SAR imagery for the Orosei Reference Map - Flood Risk Assessment Reference Map - Flood Risk Assessment Reference Map - Flood Risk Assessment Transportation Network Vulnerability to disruption Map - Flood Risk Assessment Transportation Network Vulnerability to disruption Map - Flood Risk Assessment Transportation Network Vulnerability to disruption Map - Flood Risk Assessment Assets Vulnerability Map - Flood Risk Assessment Assets Vulnerability Map - Flood Risk Assessment Assets Vulnerability Map - Flood Risk Assessment Assets and Trans. Networks at Risk Map - Flood Risk Assessment</t>
+Observed flood extent mapping was estimated using the available SAR imagery for the Orosei sub AOI, which cover Reference Map - Flood Risk Assessment Damage assessment Map - Flooding at peak conditions Transportation Network Vulnerability to disruption Map - Flood Risk Assessment Transportation Network Vulnerability to disruption Map - Flood Risk Assessment Transportation Network Vulnerability to disruption Map - Flood Risk Assessment Assets Vulnerability Map - Flood Risk Assessment Assets Vulnerability Map - Flood Risk Assessment Assets Vulnerability Map - Flood Risk Assessment Assets and Trans. Networks at Risk Map - Flood Risk Assessment Assets and Trans. Networks at Risk Map - Flood Risk Assessment</t>
         </is>
       </c>
     </row>
@@ -40841,8 +41075,7 @@
         <is>
           <t>The scope of the service request was to generate reference information, concerning flood events that occurred from July 25 to July 27 2017, within the Hildesheim district of the Lower Saxony State of Germany. General Reference content and Land Use/Cover products were produced along with flood specific products:
 Estimated Maximum Flood Extent
-[Image: 18_59_04.png]
-Theobserved flood extentproduct was generated by appropriate processing of relevant SAR imagery during and after the flood ev Estimated maximum flood extent Map - Detailed Flood Delineation in Hildesheim Land Use and Land Cover Map - Detailed flood delineation in Hildesheim Reference Map - Detailed flood delineation in Hildesheim</t>
+Theobserved flood extentproduct was generated by appropriate processing of relevant SAR imagery during and after the flood event. A classification Estimated maximum flood extent Map Land Use and Land Cover Map Reference Map</t>
         </is>
       </c>
     </row>
@@ -41263,8 +41496,7 @@
         <is>
           <t>The scope of the service request was to generate Forest Fire Risk assessment analyses and mitigation products covering a set of 27 focus areas in Croatia. Apart from the General Reference context the following Risk and Recovery products were generated:
 Assets &amp; Population Exposure &amp; Vulnerability
-[Image: 18_34_24.png]
-The assessment of the forest firehazardtakes in to account both fire intensity and surface properties. The generation of a forest fire index layer was based on specific as Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment</t>
+The assessment of the forest firehazardtakes in to account both fire intensity and surface properties. The generation of a forest fire index layer was based on specific assumptions and takes i Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment Population, Assets &amp; Transportation Network at Risk Map - Forest Fires Risk Assessment</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41924,7 @@
       <c r="M735" t="inlineStr">
         <is>
           <t>Pre-disaster situation analyses for four locations in Italy: Priolo (Sicilia), Otranto (Puglia), Metaponto (Basilicatta) and Catanzaro Lido (Calabria). All of the AOIs are located on the coast, on the front line of any eventual tsunami. A correct and detailed capture of assets was essential in order to improve and perform detailed response and evacuation programs and  in order to minimize casualties in a disaster situation.
-The scope of the map production is to generate a pre-event reference co Transport Capacity (Overview A1) Transport Capacity (Overview A1) Transport Capacity (Overview A1) Transport Capacity (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Land Cover Land Use map (Overview A1) Land Cover Land Use map (Overview A1)</t>
+The scope of the map production is to generate a pre-event reference co Reference map Transport Capacity Transport Capacity Transport Capacity Transport Capacity Reference map Reference map Reference map Land Cover Land Use map Land Cover Land Use map</t>
         </is>
       </c>
     </row>
@@ -42085,10 +42317,8 @@
 … To generate comprehensive knowledge for
 Key user: UNESCO, Section on Earth Sciences &amp; Geo-Hazards Risk Reduction
 UNESCO projects Support:
-[Image: 17_45_41.png]
 Potential Severity of the RisksGeneration of Detailed (1:5000 mapping scale) Thematic Information to assist/focus contingency planning towards minimizing loss of life &amp; damages.
-[Image: 17_51_48.png]
-Earthquake: Probabilistic seismic hazard ( Seismic Hazard &amp; Assets Exposure Map - Seismic Risk Assessment Seismic Hazard &amp; Assets Exposure Map - Seismic Risk Assessment Seismic Hazard &amp; Assets Exposure Map - Seismic Risk Assessment</t>
+Earthquake: Probabilistic seismic hazard (PSHA); mean PGA values for 10% probability Seismic Hazard &amp; Assets Exposure Map - Seismic Risk Assessment Seismic Hazard &amp; Assets Exposure Map - Seismic Risk Assessment Seismic Hazard &amp; Assets Exposure Map - Seismic Risk Assessment</t>
         </is>
       </c>
     </row>
@@ -44114,7 +44344,7 @@
         <is>
           <t>Service Request: Help assess the impact of the May-June 2016 flooding, through post-disaster situation analyses, on the agricultural sector within the vast Centre – Val-de-Loire area of interest. During the episode some areas experienced the worst flooding in 100 years. The activation covers mapping the event, damage grading and economic impact focusing on agriculture sector to provide direct support in public policy implementation by the Ministry of Agriculture.
 Proposed solution and results:
- - Val de Loire : Impact on the Agricultural Sector - Val de Loire : Impact on Land Cover - Val de Loire : Maximum Flood Extent</t>
+ Impact on the agricultural sector Impact on land cover Maximum flood extent</t>
         </is>
       </c>
     </row>
@@ -44278,7 +44508,7 @@
       <c r="L781" t="inlineStr"/>
       <c r="M781" t="inlineStr">
         <is>
-          <t>EMSN034 is a pre-disaster situation analyses to provide thematic information supporting planning for contingencies on vulnerable coastal areas along with a European framework directive on the assessment and management of the flood risk (2007/60/EC). Area of interest is 14 kilometres of beaches in Costa da Caparica, 10 km south of Lisbon, and the belt of land of with width of 1,5 km, along the shore line. Main earth observation data, imagery and digital elevation models, were provided by the acti Reference map (Overview A1) Mitigation Measures (Overview A1) Socio-Economic Vulnerability Methodology 2 (Overview A1) Physical Vulnerability Methodology 2 (Overview A1) Socio-Economic Risk Methodology 2 (Overview A1) Physical Risk Methodology 2 (Overview A1) Coastal Flood Hazard Methodology 2 (Overview A1) Coastal Flood Risk Frequent Scenario T=5 (Overview A1) Coastal Flood Risk Remote Scenario T=50 (Overview A1) Coastal Flood Risk Occasional Scenario T=25 (Overview A1)</t>
+          <t>EMSN034 is a pre-disaster situation analyses to provide thematic information supporting planning for contingencies on vulnerable coastal areas along with a European framework directive on the assessment and management of the flood risk (2007/60/EC). Area of interest is 14 kilometres of beaches in Costa da Caparica, 10 km south of Lisbon, and the belt of land of with width of 1,5 km, along the shore line. Main earth observation data, imagery and digital elevation models, were provided by the acti Reference map Mitigation Measures Socio-Economic Vulnerability Methodology 2 Physical Vulnerability Methodology 2 Socio-Economic Risk Methodology 2 Physical Risk Methodology 2 Coastal Flood Hazard Methodology 2 Coastal Flood Risk Frequent Scenario T=5 Coastal Flood Risk Remote Scenario T=50 Coastal Flood Risk Occasional Scenario T=25</t>
         </is>
       </c>
     </row>
@@ -44456,119 +44686,118 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
+          <t>EMSN038</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Peru'}]</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Post-disaster situation analyses of flood and landslides in Lima, Peru</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>POINT (-76.95929999999998 -11.886920000000007)</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>2017-03-08T01:00:00</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>2026-01-20T09:57:00.365888</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I785" t="b">
+        <v>1</v>
+      </c>
+      <c r="J785" t="n">
+        <v>1</v>
+      </c>
+      <c r="K785" t="n">
+        <v>5</v>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
+The scope of the map production is t...</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
+The scope of the map production is to generate a pre-event reference content, delineate the event impact and grade the damage, focusing on people and assets, with particular attention to schools in the metropolitan area  of northern Lima Reference map Land Use / Land Cover map Landslide extent delineation Flood extent delineation Damage assessment - Flood</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
           <t>EMSN033</t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>[{'short_name': 'Libya'}]</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
-      <c r="D785" t="inlineStr">
+      <c r="D786" t="inlineStr">
         <is>
           <t>Satellite based conflict damage assessment of two selected cities in Libya</t>
         </is>
       </c>
-      <c r="E785" t="inlineStr">
+      <c r="E786" t="inlineStr">
         <is>
           <t>POINT (21.79769 28.28583)</t>
         </is>
       </c>
-      <c r="F785" t="inlineStr">
+      <c r="F786" t="inlineStr">
         <is>
           <t>2017-03-08T01:00:00</t>
         </is>
       </c>
-      <c r="G785" t="inlineStr"/>
-      <c r="H785" t="inlineStr">
+      <c r="G786" t="inlineStr"/>
+      <c r="H786" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="I785" t="b">
-        <v>1</v>
-      </c>
-      <c r="J785" t="n">
+      <c r="I786" t="b">
+        <v>1</v>
+      </c>
+      <c r="J786" t="n">
         <v>3</v>
       </c>
-      <c r="K785" t="n">
+      <c r="K786" t="n">
         <v>68</v>
       </c>
-      <c r="L785" t="inlineStr"/>
-      <c r="M785" t="inlineStr">
+      <c r="L786" t="inlineStr"/>
+      <c r="M786" t="inlineStr">
         <is>
           <t>EMSN033 is a satellite based conflict damage assessment of three selected areas of interest (AOIs) in Libya: Benghazi city, Benghazi´s Aerodrome (El Benina) and Al-Jawf.
 The scope of the map production was to generate general reference content of the pre-event situation, including administrative boundaries, road network, urban land use classification, urban sprawl and urban expansion velocity analysis.
-The core users of the map are the Foreign Policy Instruments (FPI) of the European Commi Urban velocity map (Overview A1) Urban velocity map (Overview A1) Urban Sprawl map (Overview A1) Urban Sprawl map (Overview A1) Urban Sprawl map (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Reference map (Detail B2) Reference map (Detail B2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>EMSN038</t>
-        </is>
-      </c>
-      <c r="B786" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Peru'}]</t>
-        </is>
-      </c>
-      <c r="C786" t="inlineStr">
-        <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
-        </is>
-      </c>
-      <c r="D786" t="inlineStr">
-        <is>
-          <t>Post-disaster situation analyses of flood and landslides in Lima, Peru</t>
-        </is>
-      </c>
-      <c r="E786" t="inlineStr">
-        <is>
-          <t>POINT (-76.95929999999998 -11.886920000000007)</t>
-        </is>
-      </c>
-      <c r="F786" t="inlineStr">
-        <is>
-          <t>2017-03-08T01:00:00</t>
-        </is>
-      </c>
-      <c r="G786" t="inlineStr">
-        <is>
-          <t>2026-01-20T09:57:00.365888</t>
-        </is>
-      </c>
-      <c r="H786" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I786" t="b">
-        <v>1</v>
-      </c>
-      <c r="J786" t="n">
-        <v>1</v>
-      </c>
-      <c r="K786" t="n">
-        <v>5</v>
-      </c>
-      <c r="L786" t="inlineStr">
-        <is>
-          <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
-The scope of the map production is t...</t>
-        </is>
-      </c>
-      <c r="M786" t="inlineStr">
-        <is>
-          <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
-The scope of the map production is to generate a pre-event reference content, delineate the event impact and grade the damage, focusing on people and assets, with particular attention to schools in the metropolitan area  of northern Lima.
- Reference map (Overview A1) Land Use / Land Cover map (Overview A1) Landslide extent delineation (Overview A1) Flood extent delineation (Overview A1) Damage assessment - Flood (Overview A1)</t>
+The core users of the map are the Foreign Policy Instruments (FPI) of the European Commi Reference map Reference map Urban velocity map Urban velocity map Urban Sprawl map Urban Sprawl map Urban Sprawl map Reference map Reference map Reference map</t>
         </is>
       </c>
     </row>
@@ -44859,7 +45088,7 @@
       <c r="M791" t="inlineStr">
         <is>
           <t>This activation focuses on damage assessment and landslide risk assessment relating to major forest fires in the municipalities of Funchal and Calheta, Madeira in August 2016. Key assets (infrastructure, environment, human life, economic sustainability, etc.) are also identified and related with the severity of impact. The service involves:
-To optimize the efficiency of the preventative measures to be implemented, risk maps (landslides) and damages maps (burnt areas, grading) at large scale ( Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment (Details, Tile 2009) Population and Assets at Risk Map - Landslide Risk Assessment (Details, Tile 2008) Population and Assets at Risk Map - Landslide Risk Assessment (Details, Tile 2007) Population and Assets at Risk Map - Landslide Risk Assessment (Details, Tile 2006) Population and Assets at Risk Map - Landslide Risk Assessment (Details, Tile 2005) Population and Assets at Risk Map - Landslide Risk Assessment (Details, Tile 2004) Population and Assets at Risk Map - Landslide Risk Assessment (Details, Tile 2003) Population and Assets at Risk Map - Landslide Risk Assessment (Details, Tile 2002)</t>
+To optimize the efficiency of the preventative measures to be implemented, risk maps (landslides) and damages maps (burnt areas, grading) at large scale ( Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment Population and Assets at Risk Map - Landslide Risk Assessment</t>
         </is>
       </c>
     </row>
@@ -45033,7 +45262,7 @@
       <c r="M794" t="inlineStr">
         <is>
           <t>EMSN030 was activated by the National Directorate General for Disaster Management, Hungary, on behalf of the EUCPT (Scoping Mission in Solotvyno salt mine, Ukraine) on 12/7/2016. The crisis related to the structural deterioration of old salt mines due to flooding of mine shafts and subsequent contamination of the Tisza River. Underground cavities and sinkholes emerged, threatening the local population, as well as industrial buildings and engineering systems.
-In order to monitor the ground def Current Trends Map - Sinkhole and Landslides Risk Map Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1004) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1003) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1002) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1001) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1004) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1003) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1002) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1001)</t>
+In order to monitor the ground def Current Trends Map - Sinkhole and Landslides Risk Map Current Trends Map - Sinkhole and Landslides Risk Map Current Trends Map - Sinkhole and Landslides Risk Map Current Trends Map - Sinkhole and Landslides Risk Map Current Trends Map - Sinkhole and Landslides Risk Map Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics</t>
         </is>
       </c>
     </row>
@@ -46042,12 +46271,10 @@
       <c r="M812" t="inlineStr">
         <is>
           <t>The scope of the service request EMSN027 was to monitor advances made in the implementation of local humanitarian recovery WFP-funded construction projects in Somalia, in particular drought mitigation measures, and to assess their impact on the surrounding vegetation recovery.
-[Image: 10_41_33.png]
 The products of the EMSN027 activation can be grouped as follows:
 Reference maps
-[Image: Untitled(3).png]
 Vegetation maps
-For the assessment of vegetation vigour and biomass, the tem Vegetation Vigour (Overview A7) Reference map (Overview A7) Reference map (Detail A7) Green Area Extent (Overview A7) Biomass (Overview A7) Vegetation Vigour (Overview A6) Reference map (Overview A6) Reference map (Detail A6) Green Area Extent (Overview A6) Biomass (Overview A6)</t>
+For the assessment of vegetation vigour and biomass, the temporal frequency of the image acquisitions was Vegetation Vigour Reference map Reference map Green Area Extent Biomass Vegetation Vigour Reference map Reference map Green Area Extent Biomass</t>
         </is>
       </c>
     </row>
@@ -46225,129 +46452,128 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
+          <t>EMSN025</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Greece'}]</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Forest fire damage assessment – Planning and Recovery</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>POINT (25.579999999999995 38.34999999999999)</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>2016-06-13T01:00:00</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>2026-01-20T09:54:14.348681</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I816" t="b">
+        <v>1</v>
+      </c>
+      <c r="J816" t="n">
+        <v>6</v>
+      </c>
+      <c r="K816" t="n">
+        <v>84</v>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>This activation focuses on damage delineation and grading maps for selected forest fires in Greece in the summer of 2015. Additionally, loss assessment and risk assessment products (landslide/erosion and flash flood) including, mitigation and recovery measures are analysed. Key assets (infrastruc...</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>This activation focuses on damage delineation and grading maps for selected forest fires in Greece in the summer of 2015. Additionally, loss assessment and risk assessment products (landslide/erosion and flash flood) including, mitigation and recovery measures are analysed. Key assets (infrastructure, environment, human life, economic sustainability, etc.) are also identified and related with the probability and severity (impact) of potential (secondary) hazards.
+The activation was triggered  Assets and Trans. Networks at Risk Map - Flood Risk Assessment Soil Loss Map - Erosion Hazard Zones Assets and Trans. Networks at Risk Map - Landslide Risk Assessment Land Use and Land Cover Map - Multiple Natural Hazard Risk Assessment Biomass Loss Assessment Map - Fire Damage Assessment Delineation and Grading Map - Fire Damage Assessment Reference Map - Multiple Natural Hazard Risk Assessment Assets and Trans. Networks at Risk Map - Flood Risk Assessment Soil Loss Map - Erosion Hazard Zones Assets and Trans. Networks at Risk Map - Landslide Risk Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
           <t>EMSN029</t>
         </is>
       </c>
-      <c r="B816" t="inlineStr">
+      <c r="B817" t="inlineStr">
         <is>
           <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
-      <c r="C816" t="inlineStr">
+      <c r="C817" t="inlineStr">
         <is>
           <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
-      <c r="D816" t="inlineStr">
+      <c r="D817" t="inlineStr">
         <is>
           <t>Forest fire damage assessment - new risks and mitigation</t>
         </is>
       </c>
-      <c r="E816" t="inlineStr">
+      <c r="E817" t="inlineStr">
         <is>
           <t>POINT (-0.54267 40.01794999999999)</t>
         </is>
       </c>
-      <c r="F816" t="inlineStr">
+      <c r="F817" t="inlineStr">
         <is>
           <t>2016-06-13T01:00:00</t>
         </is>
       </c>
-      <c r="G816" t="inlineStr">
+      <c r="G817" t="inlineStr">
         <is>
           <t>2026-01-20T09:55:03.938401</t>
         </is>
       </c>
-      <c r="H816" t="inlineStr">
+      <c r="H817" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="I816" t="b">
-        <v>1</v>
-      </c>
-      <c r="J816" t="n">
-        <v>1</v>
-      </c>
-      <c r="K816" t="n">
+      <c r="I817" t="b">
+        <v>1</v>
+      </c>
+      <c r="J817" t="n">
+        <v>1</v>
+      </c>
+      <c r="K817" t="n">
         <v>8</v>
       </c>
-      <c r="L816" t="inlineStr">
+      <c r="L817" t="inlineStr">
         <is>
           <t>Two areas of Special Areas of Conservation: Sierra de Espadn and Curs Alt del riu Millars were hit by a forest fire in July 2015, in the Montn and Caudiel municipalities of the region of Valencia. The analysis of the damage degree and landslide and erosion risk is of key importance for the spatia...</t>
         </is>
       </c>
-      <c r="M816" t="inlineStr">
+      <c r="M817" t="inlineStr">
         <is>
           <t>Two areas of Special Areas of Conservation: Sierra de Espadn and Curs Alt del riu Millars were hit by a forest fire in July 2015, in the Montn and Caudiel municipalities of the region of Valencia. The analysis of the damage degree and landslide and erosion risk is of key importance for the spatial and temporal planning of the post-event restoration work. The scope of the activation included:
 Delineation/grading
 Loss assessment
-[Image: 10_56_00.png]
 Landslide risk
 Erosion risk
-[ Reference map (Detail A1) Possible New Risk (Detail A1) Mitigation Measures: Stack and Felling (Detail A1) Mitigation Measures: Regeneration and Hydro (Detail A1) Loss assessment (Detail A1) LandSlide Risk (Detail A1) Erosion Risk (Detail A1) Damage delineation and grading (Detail A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>EMSN025</t>
-        </is>
-      </c>
-      <c r="B817" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Greece'}]</t>
-        </is>
-      </c>
-      <c r="C817" t="inlineStr">
-        <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
-        </is>
-      </c>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>Forest fire damage assessment – Planning and Recovery</t>
-        </is>
-      </c>
-      <c r="E817" t="inlineStr">
-        <is>
-          <t>POINT (25.579999999999995 38.34999999999999)</t>
-        </is>
-      </c>
-      <c r="F817" t="inlineStr">
-        <is>
-          <t>2016-06-13T01:00:00</t>
-        </is>
-      </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>2026-01-20T09:54:14.348681</t>
-        </is>
-      </c>
-      <c r="H817" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I817" t="b">
-        <v>1</v>
-      </c>
-      <c r="J817" t="n">
-        <v>6</v>
-      </c>
-      <c r="K817" t="n">
-        <v>84</v>
-      </c>
-      <c r="L817" t="inlineStr">
-        <is>
-          <t>This activation focuses on damage delineation and grading maps for selected forest fires in Greece in the summer of 2015. Additionally, loss assessment and risk assessment products (landslide/erosion and flash flood) including, mitigation and recovery measures are analysed. Key assets (infrastruc...</t>
-        </is>
-      </c>
-      <c r="M817" t="inlineStr">
-        <is>
-          <t>This activation focuses on damage delineation and grading maps for selected forest fires in Greece in the summer of 2015. Additionally, loss assessment and risk assessment products (landslide/erosion and flash flood) including, mitigation and recovery measures are analysed. Key assets (infrastructure, environment, human life, economic sustainability, etc.) are also identified and related with the probability and severity (impact) of potential (secondary) hazards.
-The activation was triggered  Assets and Trans. Networks at Risk Map - Flood Risk Assessment (Details, Tile 6011) Soil Loss Map - Erosion Hazard Zones (Details, Tile 6011) Assets and Trans. Networks at Risk Map - Landslide Risk Assessment (Details, Tile 6011) Land Use and Land Cover Map - Multiple Natural Hazard Risk Assessment (Details, Tile 6011) Biomass Loss Assessment Map - Fire Damage Assessment (Details, Tile 6011) Delineation and Grading Map - Fire Damage Assessment (Details, Tile 6011) Reference Map - Multiple Natural Hazard Risk Assessment (Details, Tile 6011) Assets and Trans. Networks at Risk Map - Flood Risk Assessment (Details, Tile 5010) Soil Loss Map - Erosion Hazard Zones (Details, Tile 5010) Assets and Trans. Networks at Risk Map - Landslide Risk Assessment (Details, Tile 5010)</t>
+Mitigation measure Reference map Possible New Risk Mitigation Measures: Stack and Felling Mitigation Measures: Regeneration and Hydro Loss assessment LandSlide Risk Erosion Risk Damage delineation and grading</t>
         </is>
       </c>
     </row>
@@ -46402,7 +46628,7 @@
         <is>
           <t>In late May and early June 2016 flooding began after several days of heavy rain. The Loing and Seine rivers burst their banks and 4,000 people were evacuated from the town of Nemours. Some areas reported the worst flooding seen in a century.
 This activation was requested by the Ministère de l’Intérieur, Direction Générale de la Sécurité Civile et de la Gestion des Crises (COGIC).
-The scope of the request is to map flooding extents, infer maximum flooding and flood water depths, and assess  Maximum Flood Extent (Detail) Maximum Flood Extent (Detail) Maximum Flood Extent (Detail) Maximum Flood Extent (Detail) Maximum Flood Extent (Detail) Maximum Flood Extent (Detail) Maximum Flood Extent (Detail) Maximum Flood Extent (Detail) Maximum Flood Extent (Detail) Maximum Flood Extent (Detail)</t>
+The scope of the request is to map flooding extents, infer maximum flooding and flood water depths, and assess  Maximum Flood Extent Maximum Flood Extent Maximum Flood Extent Maximum Flood Extent Maximum Flood Extent Maximum Flood Extent Maximum Flood Extent Maximum Flood Extent Maximum Flood Extent Maximum Flood Extent</t>
         </is>
       </c>
     </row>
@@ -46797,7 +47023,7 @@
       <c r="L825" t="inlineStr"/>
       <c r="M825" t="inlineStr">
         <is>
-          <t>Soil Loss Map - Erosion Risk Assessment Soil Loss Map - Erosion Risk Assessment (Details, Tile 1004) Soil Loss Map - Erosion Risk Assessment (Details, Tile 1003) Soil Loss Map - Erosion Risk Assessment (Details, Tile 1002) Soil Loss Map - Erosion Risk Assessment (Details, Tile 1001) Risk Map - Landslide Risk Assessment Risk Map - Landslide Risk Assessment (Details, Tile 1004) Risk Map - Landslide Risk Assessment (Details, Tile 1003) Risk Map - Landslide Risk Assessment (Details, Tile 1002) Risk Map - Landslide Risk Assessment (Details, Tile 1001)</t>
+          <t>Population at Risk Map - Flood Risk Assessment Key Dynamics: Flood Water Depth &amp; Speed Map - Flood 2014 Soil Loss Map - Erosion Risk Assessment Soil Loss Map - Erosion Risk Assessment Soil Loss Map - Erosion Risk Assessment Soil Loss Map - Erosion Risk Assessment Soil Loss Map - Erosion Risk Assessment Risk Map - Landslide Risk Assessment Risk Map - Landslide Risk Assessment Risk Map - Landslide Risk Assessment</t>
         </is>
       </c>
     </row>
@@ -46907,7 +47133,7 @@
       <c r="L827" t="inlineStr"/>
       <c r="M827" t="inlineStr">
         <is>
-          <t>Lagiewniki: Flood risk map (1 in 10 year probability) &amp; Levee break (Details, 20160730) Lagiewniki: Flood risk map (1 in 10 year probability) (Details, 20160725) Blonia: Flood risk map (1 in 10 year probability) (Details, 20160728) Lagiewniki: Flood risk map (1 in 10 year probability) &amp; Levee break (Details, 20160801) Lagiewniki: Flood risk map (1 in 10 year probability) &amp; Levee break (Details, 20160731) Blonia: Flood risk map (1 in 10 year probability) (Details, 20160729) Brzegi: Land Use Map - Detailed Blonia: Land Use Map - Detailed Brzegi: Flood risk map (1 in 10 year probability) &amp; Levee break (Details, 20160801) Brzegi: Flood risk map (1 in 10 year probability) &amp; Levee break (Details, 20160731)</t>
+          <t>Lagiewniki: Satellite Image map Blonia: Flood risk map (1 in 10 year probability) &amp; Levee break Blonia: Flood risk map (1 in 10 year probability) Lagiewniki: Flood risk map (1 in 10 year probability) &amp; Levee break Lagiewniki: Flood risk map (1 in 10 year probability) Blonia: Flood risk map (1 in 10 year probability) Brzegi: Land Use Map - Detailed Blonia: Land Use Map - Detailed Brzegi: Flood risk map (1 in 10 year probability) &amp; Levee break Brzegi: Flood risk map (1 in 10 year probability) &amp; Levee break</t>
         </is>
       </c>
     </row>
@@ -47862,7 +48088,7 @@
       <c r="L844" t="inlineStr"/>
       <c r="M844" t="inlineStr">
         <is>
-          <t>Reference map (Detail A9) Reference map (Detail A8) Reference map (Detail A7) Reference map (Detail A6) Reference map (Detail A5) Reference map (Detail A4) Reference map (Detail A3b) Reference map (Detail A3a) Reference map (Detail A2b) Reference map (Detail A2a)</t>
+          <t>Reference map Reference map Reference map Reference map Reference map Reference map Reference map Reference map Reference map Reference map</t>
         </is>
       </c>
     </row>
@@ -47915,7 +48141,7 @@
       <c r="L845" t="inlineStr"/>
       <c r="M845" t="inlineStr">
         <is>
-          <t>Reference Map Land-Use Land-Cover Seismic Hazard Seismic Risk - Population Risk Seismic Risk - Vulnerability Forest Fire - Population Risk Tsunami Risk - Population and Environmental Assets Landslide Risk - Population and Transportation Risk Erosion Risk - Soil Loss Industrial Accident Risk - Population and Environmental Assets</t>
+          <t>Industrial Accident Risk - Population and Environmental Assets Reference Map Land-Use Land-Cover Seismic Hazard Seismic Risk - Population Risk Seismic Risk - Vulnerability Forest Fire - Population Risk Tsunami Risk - Population and Environmental Assets Landslide Risk - Population and Transportation Risk Erosion Risk - Soil Loss</t>
         </is>
       </c>
     </row>
@@ -49921,7 +50147,7 @@
       <c r="L879" t="inlineStr"/>
       <c r="M879" t="inlineStr">
         <is>
-          <t>Landslide Map (Detail 4) Landslide Map (Detail 3) Landslide Map (Detail 2) Landslide Map (Detail 1) Landslide Map Erosion Map (Detail 4) Erosion Map (Detail 3) Erosion Map (Detail 2) Erosion Map (Detail 1) Erosion Map</t>
+          <t>Landslide Map Landslide Map Landslide Map Landslide Map Landslide Map Erosion Map Erosion Map Erosion Map Erosion Map Erosion Map</t>
         </is>
       </c>
     </row>
@@ -49978,7 +50204,7 @@
       <c r="L880" t="inlineStr"/>
       <c r="M880" t="inlineStr">
         <is>
-          <t>Mitigation Measures Map (Detail 02 - Guanay) Mitigation Measures Map (Detail 01 - Rurrenabaque) Mitigation Measures Map (Detail 02 - Santa Ana) Mitigation Measures Map (Detail 01 - Trinidad) Evacuation Plan (Detail 02 - Guanay) Evacuation Plan (Detail 01 - Rurrenabaque) Economic Vulnerability Map (Detail 02 - Guanay) Economic Vulnerability Map (Detail 01 - Rurrenabaque) Population Vulnerability Map (Detail 02 - Guanay) Population Vulnerability Map (Detail 01 - Rurrenabaque)</t>
+          <t>Mitigation Measures Map Mitigation Measures Map Mitigation Measures Map Mitigation Measures Map Evacuation Plan Evacuation Plan Economic Vulnerability Map Economic Vulnerability Map Population Vulnerability Map Population Vulnerability Map</t>
         </is>
       </c>
     </row>
@@ -50438,7 +50664,7 @@
       <c r="L888" t="inlineStr"/>
       <c r="M888" t="inlineStr">
         <is>
-          <t>Preparedness, disaster risk assessment and disaster risk reduction covering districts of: Kachin and Shan North Reference map (Overview C2) Reference map (Overview C1) Reference map (Overview B1) Reference map (Overview A1) Trafficability map - Fair weather (Overview C2) Trafficability map - Fair weather (Overview C1) Trafficability map - Fair weather (Overview B1) Trafficability map - Fair weather (Overview A1) Trafficability map - Adverse weather (Overview C2) Trafficability map - Adverse weather (Overview C1)</t>
+          <t>Preparedness, disaster risk assessment and disaster risk reduction covering districts of: Kachin and Shan North Reference map Reference map Reference map Reference map Trafficability map - Fair weather Trafficability map - Fair weather Trafficability map - Fair weather Trafficability map - Fair weather Trafficability map - Adverse weather Trafficability map - Adverse weather</t>
         </is>
       </c>
     </row>
@@ -51011,7 +51237,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>EMSR084</t>
+          <t>EMSR085</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -51021,17 +51247,17 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>{'slug': 'industrial', 'name': 'Industrial Accident'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>LuModExercise - Industrial accident</t>
+          <t>LuModExercise - Flood in Mertert- Luxembourg</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>POINT (6.44 49.8)</t>
+          <t>POINT (6.47 49.69)</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
@@ -51041,7 +51267,7 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>2014-05-30T17:11:00</t>
+          <t>2014-05-28T12:18:00</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
@@ -51061,14 +51287,14 @@
       <c r="L899" t="inlineStr"/>
       <c r="M899" t="inlineStr">
         <is>
-          <t>Echternach Reference Echternach Reference</t>
+          <t>Mertert Reference Mertert Reference</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>EMSR085</t>
+          <t>EMSR084</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -51078,17 +51304,17 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'industrial', 'name': 'Industrial Accident'}</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>LuModExercise - Flood in Mertert- Luxembourg</t>
+          <t>LuModExercise - Industrial accident</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>POINT (6.47 49.69)</t>
+          <t>POINT (6.44 49.8)</t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
@@ -51098,7 +51324,7 @@
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>2014-05-28T12:18:00</t>
+          <t>2014-05-30T17:11:00</t>
         </is>
       </c>
       <c r="H900" t="inlineStr">
@@ -51118,7 +51344,7 @@
       <c r="L900" t="inlineStr"/>
       <c r="M900" t="inlineStr">
         <is>
-          <t>Mertert Reference Mertert Reference</t>
+          <t>Echternach Reference Echternach Reference</t>
         </is>
       </c>
     </row>
@@ -51414,12 +51640,12 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>EMSN024</t>
+          <t>EMSN040</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Germany'}]</t>
+          <t>[{'short_name': 'Finland'}]</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -51429,12 +51655,12 @@
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Basic European Assets Map, Germany</t>
+          <t>Basic European Assets Map, Finland</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>POINT (10.44768 51.16338)</t>
+          <t>POINT (25.74815 61.92411)</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
@@ -51460,19 +51686,19 @@
       <c r="L906" t="inlineStr"/>
       <c r="M906" t="inlineStr">
         <is>
-          <t>Risk analysis for natural hazard topics, damage assessment Asset Map Germany</t>
+          <t>Service Request: The nation-wide asset mapping for Finland provides a detailed regional geospatial dataset for the quick and uncomplicated calculation of potential damages either in the preparedness phase or during the immediate response phase of crises caused by natural hazard events. The concept follows the Basic European Asset Map (BEAM) data model developed under the Copernicus precursor project SAFER (Services and Applications for Emergency Response) and extended in the FP7 project IncREO ( BEAM V2 2012 Finland</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>EMSN040</t>
+          <t>EMSN024</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Finland'}]</t>
+          <t>[{'short_name': 'Germany'}]</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -51482,12 +51708,12 @@
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Basic European Assets Map, Finland</t>
+          <t>Basic European Assets Map, Germany</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>POINT (25.74815 61.92411)</t>
+          <t>POINT (10.44768 51.16338)</t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
@@ -51513,7 +51739,7 @@
       <c r="L907" t="inlineStr"/>
       <c r="M907" t="inlineStr">
         <is>
-          <t>Service Request: The nation-wide asset mapping for Finland provides a detailed regional geospatial dataset for the quick and uncomplicated calculation of potential damages either in the preparedness phase or during the immediate response phase of crises caused by natural hazard events. The concept follows the Basic European Asset Map (BEAM) data model developed under the Copernicus precursor project SAFER (Services and Applications for Emergency Response) and extended in the FP7 project IncREO ( BEAM V2 2012 Finland</t>
+          <t>Risk analysis for natural hazard topics, damage assessment Asset Map Germany</t>
         </is>
       </c>
     </row>
@@ -51733,7 +51959,7 @@
       <c r="L911" t="inlineStr"/>
       <c r="M911" t="inlineStr">
         <is>
-          <t>Distance Index Analysis (Overview 26b) Distance Index Analysis (Overview 26a) Vegetation Density Index (Overview 25) Hagadera/Kambioos study (Detail 27) Degradation severity index (Overview 23) Degradation severity index (Overview 21) Degradation severity index (Overview 19) Degradation severity index (Overview 17) Degradation severity index (Detail 24) Degradation severity index (Detail 22)</t>
+          <t>Distance Index Analysis Distance Index Analysis Vegetation Density Index Hagadera/Kambioos study Degradation severity index Degradation severity index Degradation severity index Degradation severity index Degradation severity index Degradation severity index</t>
         </is>
       </c>
     </row>
@@ -53064,7 +53290,7 @@
       <c r="L934" t="inlineStr"/>
       <c r="M934" t="inlineStr">
         <is>
-          <t>Delineation Map Delineation Map Reference Map Reference Map Delineation Map (Detail 4, Industrial Zone) Reference Map (Detail 4, Industrial Zone) Delineation Map (Detail 2, Palinuro) Reference Map (Detail 2, Palinuro) Delineation Map (Detail 1, Marina di Camerota) Reference Map (Detail 1, Vietri Sul Mare)</t>
+          <t>Reference Map Delineation Map Delineation Map Reference Map Delineation Map Reference Map Delineation Map Reference Map Delineation Map Reference Map</t>
         </is>
       </c>
     </row>
@@ -53242,27 +53468,27 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>EMSN006</t>
+          <t>EMSN005</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Czechia'}]</t>
+          <t>[{'short_name': 'Austria'}]</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>{'slug': 'storm', 'name': 'Storm'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>Civil Protection Exercise: RESTART 2013</t>
+          <t>EU Civil Protection Exercise: EU TARANIS 2013</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>POINT (15.9473 49.95137)</t>
+          <t>POINT (13.06265 47.81082)</t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
@@ -53280,42 +53506,42 @@
         <v>1</v>
       </c>
       <c r="J938" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K938" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L938" t="inlineStr"/>
       <c r="M938" t="inlineStr">
         <is>
-          <t>Delineation Map Reference Map Reference Map Reference Map Delineation Map (Detail 5) Delineation Map (Detail 4) Delineation Map (Detail 2) Delineation Map (Detail 1) Delineation Map  Reference Map  (Detail 5)</t>
+          <t>Delineation Map Delineation Map Delineation Map Delineation Map Reference Map Reference Map Reference Map Reference Map</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>EMSN005</t>
+          <t>EMSN006</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Austria'}]</t>
+          <t>[{'short_name': 'Czechia'}]</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'storm', 'name': 'Storm'}</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>EU Civil Protection Exercise: EU TARANIS 2013</t>
+          <t>Civil Protection Exercise: RESTART 2013</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>POINT (13.06265 47.81082)</t>
+          <t>POINT (15.9473 49.95137)</t>
         </is>
       </c>
       <c r="F939" t="inlineStr">
@@ -53333,15 +53559,15 @@
         <v>1</v>
       </c>
       <c r="J939" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K939" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L939" t="inlineStr"/>
       <c r="M939" t="inlineStr">
         <is>
-          <t>Delineation Map (Detail 3) Delineation Map Delineation Map (Detail 2) Delineation Map (Detail 1) Reference Map (Detail 3) Reference Map (Detail 2) Reference Map (Detail 1) Reference Map</t>
+          <t>Delineation Map Reference Map Reference Map Reference Map Delineation Map Delineation Map Delineation Map Delineation Map Delineation Map Reference Map</t>
         </is>
       </c>
     </row>
@@ -53508,7 +53734,7 @@
       <c r="L942" t="inlineStr"/>
       <c r="M942" t="inlineStr">
         <is>
-          <t>Delineation (Detail 6) Delineation (Detail 5) Delineation (Detail 4) Delineation (Detail 3) Delineation (Detail 2) Delineation (Detail 1) Delineation</t>
+          <t>Delineation Delineation Delineation Delineation Delineation Delineation Delineation</t>
         </is>
       </c>
     </row>
@@ -54408,7 +54634,7 @@
       <c r="L958" t="inlineStr"/>
       <c r="M958" t="inlineStr">
         <is>
-          <t>Land Use Map (Detail, Sheet F3) Land Use Map (Detail, Sheet F2) Land Use Map (Detail, Sheet E4) Land Use Map (Detail, Sheet E3) Land Use Map (Detail, Sheet E2) Land Use Map (Detail, Sheet D5) Land Use Map (Detail, Sheet D4) Land Use Map (Detail, Sheet D3) Land Use Map (Detail, Sheet D2) Land Use Map (Detail, Sheet D1)</t>
+          <t>Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map</t>
         </is>
       </c>
     </row>
@@ -54461,7 +54687,7 @@
       <c r="L959" t="inlineStr"/>
       <c r="M959" t="inlineStr">
         <is>
-          <t>The International Committee of the Red Cross is requesting the non-rush GIO-EMS service to characterize the built-up of the Darfur (Sudan) cities of Al Geneina and El Daein. The purpose of the requested analysis is to map the informal and formal settlements and the non-residential city structures to derive population estimates and population densities per sector to facilitate the planning and estimation of the needs for an urban water network. Land Use Map (Detail C4) Land Use Map (Detail D2) Land Use Map (Detail D3) Land Use Map (Detail D3) Land Use Map Land Use Map Land Use Map (Detail C3) Land Use Map (Detail B2) Land Use Map (Detail E1) Land Use Map (Detail E2)</t>
+          <t>The International Committee of the Red Cross is requesting the non-rush GIO-EMS service to characterize the built-up of the Darfur (Sudan) cities of Al Geneina and El Daein. The purpose of the requested analysis is to map the informal and formal settlements and the non-residential city structures to derive population estimates and population densities per sector to facilitate the planning and estimation of the needs for an urban water network. Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map Land Use Map</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2025-09-19T07:35:38.733860</t>
+          <t>2026-10-19T12:27:39.010420</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>EMSN110</t>
+          <t>EMSN108</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -22075,12 +22075,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Wildfire in Alburquerque, Spain</t>
+          <t>Wildfire in San Felices de los Gallegos, Spain</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>POINT (-6.85472 40.02093)</t>
+          <t>POINT (-6.67526 40.8026)</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -22105,19 +22105,19 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>EMSN108</t>
+          <t>EMSN109</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -22132,12 +22132,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Wildfire in San Felices de los Gallegos, Spain</t>
+          <t>Wildfire in Alcaracejos, Spain</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>POINT (-6.67526 40.8026)</t>
+          <t>POINT (-4.94932 38.2282)</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -22162,19 +22162,19 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>EMSN109</t>
+          <t>EMSN110</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -22189,12 +22189,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Wildfire in Alcaracejos, Spain</t>
+          <t>Wildfire in Alburquerque, Spain</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>POINT (-4.94932 38.2282)</t>
+          <t>POINT (-6.85472 40.02093)</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23548,27 +23548,27 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>EMSN103</t>
+          <t>EMSN102</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Central African Republic'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>IDP camp monitoring in Bria, Central African Republic</t>
+          <t>Wildfires in Huelva, Spain</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>POINT (21.9657 6.54857)</t>
+          <t>POINT (-6.61875 37.43943)</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -23589,43 +23589,43 @@
         <v>1</v>
       </c>
       <c r="K415" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d Population displacement location Overview Map Overview Map Population displacement location</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EMSN102</t>
+          <t>EMSN103</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Spain'}]</t>
+          <t>[{'short_name': 'Central African Republic'}]</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Wildfires in Huelva, Spain</t>
+          <t>IDP camp monitoring in Bria, Central African Republic</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>POINT (-6.61875 37.43943)</t>
+          <t>POINT (21.9657 6.54857)</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -23646,16 +23646,16 @@
         <v>1</v>
       </c>
       <c r="K416" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d Population displacement location Overview Map Overview Map Population displacement location</t>
         </is>
       </c>
     </row>
@@ -23776,7 +23776,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EMSN100</t>
+          <t>EMSN101</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -23791,12 +23791,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Wildfires in La Rioja, Spain</t>
+          <t>Wildfire in Ciudad Real, Spain</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>POINT (-2.01861 42.15347)</t>
+          <t>POINT (-4.85493 38.75007)</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -23821,19 +23821,19 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>EMSN101</t>
+          <t>EMSN100</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -23848,12 +23848,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Wildfire in Ciudad Real, Spain</t>
+          <t>Wildfires in La Rioja, Spain</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>POINT (-4.85493 38.75007)</t>
+          <t>POINT (-2.01861 42.15347)</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -23878,12 +23878,12 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -24817,118 +24817,118 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
+          <t>EMSN091</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Philippines'}]</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Assessing changes in subsidence rates in the low Pampanga river basin and Manila area, Philippines</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>POINT (120.7985 14.78801)</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2021-04-30T01:00:00</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I437" t="b">
+        <v>1</v>
+      </c>
+      <c r="J437" t="n">
+        <v>1</v>
+      </c>
+      <c r="K437" t="n">
+        <v>1</v>
+      </c>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>The service was activated by a request from the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) – authorized user, and the University of Philippines – local user. Several sources suggest that the Manila NCR and lower Pampanga river basin, Philippines, has been affected by ground subsidence phenomena impacting settlements and increasing flood risk.
+The EMS service aims to provide evidence of ground moti Ground Deformation – Overview key map</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
           <t>EMSN093</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
+      <c r="B438" t="inlineStr">
         <is>
           <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
+      <c r="C438" t="inlineStr">
         <is>
           <t>{'slug': 'mass', 'name': 'Mass Movement'}</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
+      <c r="D438" t="inlineStr">
         <is>
           <t>Rockfall risk analysis in Valle Gran Rey, La Gomera (Spain)</t>
         </is>
       </c>
-      <c r="E437" t="inlineStr">
+      <c r="E438" t="inlineStr">
         <is>
           <t>POINT (-17.31476 28.102249999999998)</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr">
+      <c r="F438" t="inlineStr">
         <is>
           <t>2021-04-30T01:00:00</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr">
+      <c r="G438" t="inlineStr">
         <is>
           <t>2026-01-20T10:00:57.435407</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
+      <c r="H438" t="inlineStr">
         <is>
           <t>preparedness</t>
         </is>
       </c>
-      <c r="I437" t="b">
-        <v>1</v>
-      </c>
-      <c r="J437" t="n">
-        <v>1</v>
-      </c>
-      <c r="K437" t="n">
+      <c r="I438" t="b">
+        <v>1</v>
+      </c>
+      <c r="J438" t="n">
+        <v>1</v>
+      </c>
+      <c r="K438" t="n">
         <v>6</v>
       </c>
-      <c r="L437" t="inlineStr">
+      <c r="L438" t="inlineStr">
         <is>
           <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering i...</t>
         </is>
       </c>
-      <c r="M437" t="inlineStr">
+      <c r="M438" t="inlineStr">
         <is>
           <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering information on the potential hazard of the area, to carry out the adequate management plans.
 The products resulting from this activation are:
 Product 2
 Pre-event DEM extracted using photogrammetr Rockfall hazard. Overview key map Rockfall asset and population risk (low season). Overview key map Rockfall asset and population risk (high season). Overview key map Rockfall asset and population exposure. Overview key map Reference. Overview key map Ground Deformation. Overview key map</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>EMSN091</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Philippines'}]</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>Assessing changes in subsidence rates in the low Pampanga river basin and Manila area, Philippines</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>POINT (120.7985 14.78801)</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>2021-04-30T01:00:00</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I438" t="b">
-        <v>1</v>
-      </c>
-      <c r="J438" t="n">
-        <v>1</v>
-      </c>
-      <c r="K438" t="n">
-        <v>1</v>
-      </c>
-      <c r="L438" t="inlineStr"/>
-      <c r="M438" t="inlineStr">
-        <is>
-          <t>The service was activated by a request from the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) – authorized user, and the University of Philippines – local user. Several sources suggest that the Manila NCR and lower Pampanga river basin, Philippines, has been affected by ground subsidence phenomena impacting settlements and increasing flood risk.
-The EMS service aims to provide evidence of ground moti Ground Deformation – Overview key map</t>
         </is>
       </c>
     </row>
@@ -44686,27 +44686,27 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>EMSN038</t>
+          <t>EMSN033</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Peru'}]</t>
+          <t>[{'short_name': 'Libya'}]</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>Post-disaster situation analyses of flood and landslides in Lima, Peru</t>
+          <t>Satellite based conflict damage assessment of two selected cities in Libya</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>POINT (-76.95929999999998 -11.886920000000007)</t>
+          <t>POINT (21.79769 28.28583)</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
@@ -44714,11 +44714,7 @@
           <t>2017-03-08T01:00:00</t>
         </is>
       </c>
-      <c r="G785" t="inlineStr">
-        <is>
-          <t>2026-01-20T09:57:00.365888</t>
-        </is>
-      </c>
+      <c r="G785" t="inlineStr"/>
       <c r="H785" t="inlineStr">
         <is>
           <t>recovery</t>
@@ -44728,76 +44724,80 @@
         <v>1</v>
       </c>
       <c r="J785" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K785" t="n">
-        <v>5</v>
-      </c>
-      <c r="L785" t="inlineStr">
-        <is>
-          <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
-The scope of the map production is t...</t>
-        </is>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="L785" t="inlineStr"/>
       <c r="M785" t="inlineStr">
-        <is>
-          <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
-The scope of the map production is to generate a pre-event reference content, delineate the event impact and grade the damage, focusing on people and assets, with particular attention to schools in the metropolitan area  of northern Lima Reference map Land Use / Land Cover map Landslide extent delineation Flood extent delineation Damage assessment - Flood</t>
-        </is>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>EMSN033</t>
-        </is>
-      </c>
-      <c r="B786" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Libya'}]</t>
-        </is>
-      </c>
-      <c r="C786" t="inlineStr">
-        <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
-        </is>
-      </c>
-      <c r="D786" t="inlineStr">
-        <is>
-          <t>Satellite based conflict damage assessment of two selected cities in Libya</t>
-        </is>
-      </c>
-      <c r="E786" t="inlineStr">
-        <is>
-          <t>POINT (21.79769 28.28583)</t>
-        </is>
-      </c>
-      <c r="F786" t="inlineStr">
-        <is>
-          <t>2017-03-08T01:00:00</t>
-        </is>
-      </c>
-      <c r="G786" t="inlineStr"/>
-      <c r="H786" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I786" t="b">
-        <v>1</v>
-      </c>
-      <c r="J786" t="n">
-        <v>3</v>
-      </c>
-      <c r="K786" t="n">
-        <v>68</v>
-      </c>
-      <c r="L786" t="inlineStr"/>
-      <c r="M786" t="inlineStr">
         <is>
           <t>EMSN033 is a satellite based conflict damage assessment of three selected areas of interest (AOIs) in Libya: Benghazi city, Benghazi´s Aerodrome (El Benina) and Al-Jawf.
 The scope of the map production was to generate general reference content of the pre-event situation, including administrative boundaries, road network, urban land use classification, urban sprawl and urban expansion velocity analysis.
 The core users of the map are the Foreign Policy Instruments (FPI) of the European Commi Reference map Reference map Urban velocity map Urban velocity map Urban Sprawl map Urban Sprawl map Urban Sprawl map Reference map Reference map Reference map</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>EMSN038</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Peru'}]</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Post-disaster situation analyses of flood and landslides in Lima, Peru</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>POINT (-76.95929999999998 -11.886920000000007)</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>2017-03-08T01:00:00</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>2026-01-20T09:57:00.365888</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I786" t="b">
+        <v>1</v>
+      </c>
+      <c r="J786" t="n">
+        <v>1</v>
+      </c>
+      <c r="K786" t="n">
+        <v>5</v>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
+The scope of the map production is t...</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
+The scope of the map production is to generate a pre-event reference content, delineate the event impact and grade the damage, focusing on people and assets, with particular attention to schools in the metropolitan area  of northern Lima Reference map Land Use / Land Cover map Landslide extent delineation Flood extent delineation Damage assessment - Flood</t>
         </is>
       </c>
     </row>
@@ -51640,12 +51640,12 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>EMSN040</t>
+          <t>EMSN024</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Finland'}]</t>
+          <t>[{'short_name': 'Germany'}]</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -51655,12 +51655,12 @@
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Basic European Assets Map, Finland</t>
+          <t>Basic European Assets Map, Germany</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>POINT (25.74815 61.92411)</t>
+          <t>POINT (10.44768 51.16338)</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
@@ -51686,19 +51686,19 @@
       <c r="L906" t="inlineStr"/>
       <c r="M906" t="inlineStr">
         <is>
-          <t>Service Request: The nation-wide asset mapping for Finland provides a detailed regional geospatial dataset for the quick and uncomplicated calculation of potential damages either in the preparedness phase or during the immediate response phase of crises caused by natural hazard events. The concept follows the Basic European Asset Map (BEAM) data model developed under the Copernicus precursor project SAFER (Services and Applications for Emergency Response) and extended in the FP7 project IncREO ( BEAM V2 2012 Finland</t>
+          <t>Risk analysis for natural hazard topics, damage assessment Asset Map Germany</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>EMSN024</t>
+          <t>EMSN040</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Germany'}]</t>
+          <t>[{'short_name': 'Finland'}]</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -51708,12 +51708,12 @@
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Basic European Assets Map, Germany</t>
+          <t>Basic European Assets Map, Finland</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>POINT (10.44768 51.16338)</t>
+          <t>POINT (25.74815 61.92411)</t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
@@ -51739,7 +51739,7 @@
       <c r="L907" t="inlineStr"/>
       <c r="M907" t="inlineStr">
         <is>
-          <t>Risk analysis for natural hazard topics, damage assessment Asset Map Germany</t>
+          <t>Service Request: The nation-wide asset mapping for Finland provides a detailed regional geospatial dataset for the quick and uncomplicated calculation of potential damages either in the preparedness phase or during the immediate response phase of crises caused by natural hazard events. The concept follows the Basic European Asset Map (BEAM) data model developed under the Copernicus precursor project SAFER (Services and Applications for Emergency Response) and extended in the FP7 project IncREO ( BEAM V2 2012 Finland</t>
         </is>
       </c>
     </row>
@@ -53468,27 +53468,27 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>EMSN005</t>
+          <t>EMSN006</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Austria'}]</t>
+          <t>[{'short_name': 'Czechia'}]</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'storm', 'name': 'Storm'}</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>EU Civil Protection Exercise: EU TARANIS 2013</t>
+          <t>Civil Protection Exercise: RESTART 2013</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>POINT (13.06265 47.81082)</t>
+          <t>POINT (15.9473 49.95137)</t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
@@ -53506,42 +53506,42 @@
         <v>1</v>
       </c>
       <c r="J938" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K938" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L938" t="inlineStr"/>
       <c r="M938" t="inlineStr">
         <is>
-          <t>Delineation Map Delineation Map Delineation Map Delineation Map Reference Map Reference Map Reference Map Reference Map</t>
+          <t>Delineation Map Reference Map Reference Map Reference Map Delineation Map Delineation Map Delineation Map Delineation Map Delineation Map Reference Map</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>EMSN006</t>
+          <t>EMSN005</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Czechia'}]</t>
+          <t>[{'short_name': 'Austria'}]</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>{'slug': 'storm', 'name': 'Storm'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>Civil Protection Exercise: RESTART 2013</t>
+          <t>EU Civil Protection Exercise: EU TARANIS 2013</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>POINT (15.9473 49.95137)</t>
+          <t>POINT (13.06265 47.81082)</t>
         </is>
       </c>
       <c r="F939" t="inlineStr">
@@ -53559,15 +53559,15 @@
         <v>1</v>
       </c>
       <c r="J939" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K939" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L939" t="inlineStr"/>
       <c r="M939" t="inlineStr">
         <is>
-          <t>Delineation Map Reference Map Reference Map Reference Map Delineation Map Delineation Map Delineation Map Delineation Map Delineation Map Reference Map</t>
+          <t>Delineation Map Delineation Map Delineation Map Delineation Map Reference Map Reference Map Reference Map Reference Map</t>
         </is>
       </c>
     </row>
